--- a/FICO/DCF_FICO.xlsx
+++ b/FICO/DCF_FICO.xlsx
@@ -46,21 +46,25 @@
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Cover Page'!$A$1:$P$25</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="10000"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="173" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -242,16 +246,6 @@
       <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000563C1"/>
-      <u val="single"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -291,7 +285,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -323,7 +317,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -435,35 +429,39 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="10" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="170" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="4" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="168" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="173" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="172" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="172" fontId="17" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="16" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="4" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="8">
@@ -483,315 +481,122 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
+          <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="0"/>
-              <a:t>Cash Flow</a:t>
+              <a:t>Unlevered Free Cash Flow</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1200" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </txPr>
     </title>
     <plotArea>
-      <layout/>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
-        <varyColors val="0"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
-              <a:schemeClr val="bg2"/>
-            </a:solidFill>
             <a:ln>
-              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <numFmt formatCode="&quot;$&quot;#,##0"/>
-            <spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg2"/>
-                    </a:solidFill>
-                    <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
           <cat>
             <numRef>
-              <f>'DCF Model'!$E$18:$I$18</f>
-              <numCache>
-                <formatCode>m/d/yyyy</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>43281</v>
-                </pt>
-                <pt idx="1">
-                  <v>43646</v>
-                </pt>
-                <pt idx="2">
-                  <v>44012</v>
-                </pt>
-                <pt idx="3">
-                  <v>44377</v>
-                </pt>
-                <pt idx="4">
-                  <v>44742</v>
-                </pt>
-              </numCache>
+              <f>'DCF Model'!$E$17:$I$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DCF Model'!$E$28:$I$28</f>
-              <numCache>
-                <formatCode>_-* #,##0_-;\(#,##0\)_-;_-* "-"_-;_-@_-</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>17747.131</v>
-                </pt>
-                <pt idx="1">
-                  <v>37715.192065</v>
-                </pt>
-                <pt idx="2">
-                  <v>41501.07372819999</v>
-                </pt>
-                <pt idx="3">
-                  <v>43510.46166568699</v>
-                </pt>
-                <pt idx="4">
-                  <v>47008.02994358224</v>
-                </pt>
-              </numCache>
+              <f>'DCF Model'!$E$26:$I$26</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="50"/>
-        <overlap val="-27"/>
-        <axId val="542849320"/>
-        <axId val="542849648"/>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
       </barChart>
-      <dateAx>
-        <axId val="542849320"/>
+      <catAx>
+        <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="yyyy" sourceLinked="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Fiscal year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </txPr>
-        <crossAx val="542849648"/>
-        <crosses val="autoZero"/>
+        <crossAx val="100"/>
         <lblOffset val="100"/>
-        <baseTimeUnit val="years"/>
-        <majorUnit val="1"/>
-        <majorTimeUnit val="years"/>
-        <minorUnit val="1"/>
-        <minorTimeUnit val="years"/>
-      </dateAx>
+      </catAx>
       <valAx>
-        <axId val="542849648"/>
+        <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
         <axPos val="l"/>
-        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD thousands</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </txPr>
-        <crossAx val="542849320"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
+        <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
+  <oneCellAnchor>
     <from>
-      <col>4</col>
-      <colOff>714376</colOff>
-      <row>3</row>
-      <rowOff>28575</rowOff>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>9</col>
-      <colOff>771525</colOff>
-      <row>14</row>
-      <rowOff>51063</rowOff>
-    </to>
+    <ext cx="5760000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -805,7 +610,7 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1076,1712 +881,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="68" t="inlineStr">
         <is>
-          <t>FICO DCF — 10-K source map (click links)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fair Isaac Corporation (FICO) | CIK 0000814547 | FYE September 30 | Units: USD thousands</t>
+          <t>FICO DCF — 10-K source links</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Click the FY2025 10-K link for each line. Naming differences (e.g. OpEx) are explained in column E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="69" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B5" s="69" t="inlineStr">
-        <is>
-          <t>Model / CFI label</t>
-        </is>
-      </c>
-      <c r="C5" s="69" t="inlineStr">
-        <is>
-          <t>CFI cell/row</t>
-        </is>
-      </c>
-      <c r="D5" s="69" t="inlineStr">
-        <is>
-          <t>FICO 10-K label (as printed)</t>
-        </is>
-      </c>
-      <c r="E5" s="69" t="inlineStr">
-        <is>
-          <t>Naming / mapping note</t>
-        </is>
-      </c>
-      <c r="F5" s="69" t="inlineStr">
-        <is>
-          <t>10-K statement section</t>
-        </is>
-      </c>
-      <c r="G5" s="69" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="H5" s="69" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="I5" s="69" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="J5" s="69" t="inlineStr">
-        <is>
-          <t>FY2025 10-K URL</t>
-        </is>
-      </c>
-      <c r="K5" s="69" t="inlineStr">
-        <is>
-          <t>FY2024 10-K URL</t>
-        </is>
-      </c>
-      <c r="L5" s="69" t="inlineStr">
-        <is>
-          <t>FY2023 10-K URL</t>
-        </is>
-      </c>
-      <c r="M5" s="69" t="inlineStr">
-        <is>
-          <t>XBRL / derivation</t>
+          <t>FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Purchases of PPE 8,922 + Capitalized internal-use software 30,485 = 39,407</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OpEx</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SG&amp;A + R&amp;D on income statement (no single OpEx line)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B6" s="70" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="C6" s="70" t="inlineStr">
-        <is>
-          <t>3S!row24 / DCF driver base</t>
-        </is>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>Same meaning. 10-K Consolidated Statements of Income: 'Revenues'.</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G6" s="70" t="n">
-        <v>1513557</v>
-      </c>
-      <c r="H6" s="70" t="n">
-        <v>1717526</v>
-      </c>
-      <c r="I6" s="70" t="n">
-        <v>1990869</v>
-      </c>
-      <c r="J6" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K6" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L6" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M6" s="70" t="inlineStr">
-        <is>
-          <t>RevenueFromContractWithCustomerExcludingAssessedTax</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B7" s="70" t="inlineStr">
-        <is>
-          <t>COGS / Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="C7" s="70" t="inlineStr">
-        <is>
-          <t>3S!row25</t>
-        </is>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
-        <is>
-          <t>Cost of revenues</t>
-        </is>
-      </c>
-      <c r="E7" s="70" t="inlineStr">
-        <is>
-          <t>CFI says COGS; FICO 10-K labels it 'Cost of revenues' (same economic line).</t>
-        </is>
-      </c>
-      <c r="F7" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G7" s="70" t="n">
-        <v>311053</v>
-      </c>
-      <c r="H7" s="70" t="n">
-        <v>348206</v>
-      </c>
-      <c r="I7" s="70" t="n">
-        <v>353722</v>
-      </c>
-      <c r="J7" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K7" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L7" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M7" s="70" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF OpEx</t>
-        </is>
-      </c>
-      <c r="B8" s="70" t="inlineStr">
-        <is>
-          <t>SG&amp;A (CFI: Salaries and Benefits)</t>
-        </is>
-      </c>
-      <c r="C8" s="70" t="inlineStr">
-        <is>
-          <t>3S!row28</t>
-        </is>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative</t>
-        </is>
-      </c>
-      <c r="E8" s="70" t="inlineStr">
-        <is>
-          <t>NAMING DIFFERS. CFI template line is 'Salaries and Benefits'. FICO 10-K has no 'Salaries' line — map FICO SG&amp;A here. OpEx in FICO ≈ SG&amp;A + R&amp;D (below).</t>
-        </is>
-      </c>
-      <c r="F8" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G8" s="70" t="n">
-        <v>400565</v>
-      </c>
-      <c r="H8" s="70" t="n">
-        <v>462834</v>
-      </c>
-      <c r="I8" s="70" t="n">
-        <v>513028</v>
-      </c>
-      <c r="J8" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K8" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L8" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M8" s="70" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF OpEx</t>
-        </is>
-      </c>
-      <c r="B9" s="70" t="inlineStr">
-        <is>
-          <t>R&amp;D (CFI: Rent and Overhead)</t>
-        </is>
-      </c>
-      <c r="C9" s="70" t="inlineStr">
-        <is>
-          <t>3S!row29</t>
-        </is>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="E9" s="70" t="inlineStr">
-        <is>
-          <t>NAMING DIFFERS. CFI 'Rent and Overhead' is a placeholder opex bucket. FICO maps R&amp;D expense into that row. Combined SG&amp;A+R&amp;D = operating expenses excl. COGS/D&amp;A.</t>
-        </is>
-      </c>
-      <c r="F9" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G9" s="70" t="n">
-        <v>159950</v>
-      </c>
-      <c r="H9" s="70" t="n">
-        <v>171940</v>
-      </c>
-      <c r="I9" s="70" t="n">
-        <v>188347</v>
-      </c>
-      <c r="J9" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K9" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L9" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M9" s="70" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopmentExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="70" t="inlineStr">
-        <is>
-          <t>DCF</t>
-        </is>
-      </c>
-      <c r="B10" s="70" t="inlineStr">
-        <is>
-          <t>Operating Expenses (SG&amp;A + R&amp;D)</t>
-        </is>
-      </c>
-      <c r="C10" s="70" t="inlineStr">
-        <is>
-          <t>used inside DCF EBIT build</t>
-        </is>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative + Research and development</t>
-        </is>
-      </c>
-      <c r="E10" s="70" t="inlineStr">
-        <is>
-          <t>FICO does not print a single 'Operating expenses' total for SG&amp;A+R&amp;D. Sum the two 10-K lines. Do NOT confuse with 'Cost of revenues'.</t>
-        </is>
-      </c>
-      <c r="F10" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G10" s="70" t="n">
-        <v>560515</v>
-      </c>
-      <c r="H10" s="70" t="n">
-        <v>634774</v>
-      </c>
-      <c r="I10" s="70" t="n">
-        <v>701375</v>
-      </c>
-      <c r="J10" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K10" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L10" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M10" s="70" t="inlineStr">
-        <is>
-          <t>SG&amp;A + R&amp;D (derived)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="70" t="inlineStr">
-        <is>
-          <t>DCF</t>
-        </is>
-      </c>
-      <c r="B11" s="70" t="inlineStr">
-        <is>
-          <t>EBIT / Operating income</t>
-        </is>
-      </c>
-      <c r="C11" s="70" t="inlineStr">
-        <is>
-          <t>DCF!E21 (and forecast)</t>
-        </is>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="E11" s="70" t="inlineStr">
-        <is>
-          <t>CFI/DCF 'EBIT' ≈ FICO 'Operating income' on the income statement.</t>
-        </is>
-      </c>
-      <c r="F11" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G11" s="70" t="n">
-        <v>642830</v>
-      </c>
-      <c r="H11" s="70" t="n">
-        <v>733629</v>
-      </c>
-      <c r="I11" s="70" t="n">
-        <v>924850</v>
-      </c>
-      <c r="J11" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K11" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L11" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M11" s="70" t="inlineStr">
-        <is>
-          <t>OperatingIncomeLoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B12" s="70" t="inlineStr">
-        <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="C12" s="70" t="inlineStr">
-        <is>
-          <t>3S!row31</t>
-        </is>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>Interest expense, net</t>
-        </is>
-      </c>
-      <c r="E12" s="70" t="inlineStr">
-        <is>
-          <t>10-K presents 'Interest expense, net' (interest expense netted with interest income). Use that printed line, not gross InterestExpense alone when they diverge.</t>
-        </is>
-      </c>
-      <c r="F12" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G12" s="70" t="n">
-        <v>95546</v>
-      </c>
-      <c r="H12" s="70" t="n">
-        <v>105638</v>
-      </c>
-      <c r="I12" s="70" t="n">
-        <v>133647</v>
-      </c>
-      <c r="J12" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K12" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L12" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M12" s="70" t="inlineStr">
-        <is>
-          <t>Interest expense, net (10-K IS line)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B13" s="70" t="inlineStr">
-        <is>
-          <t>Tax Expense / Cash Taxes rate</t>
-        </is>
-      </c>
-      <c r="C13" s="70" t="inlineStr">
-        <is>
-          <t>3S!row35; DCF!D5 tax rate</t>
-        </is>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
-      <c r="E13" s="70" t="inlineStr">
-        <is>
-          <t>Tax expense from income statement. DCF cash-tax rate uses FY25 tax / pretax approx.</t>
-        </is>
-      </c>
-      <c r="F13" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G13" s="70" t="n">
-        <v>124249</v>
-      </c>
-      <c r="H13" s="70" t="n">
-        <v>129214</v>
-      </c>
-      <c r="I13" s="70" t="n">
-        <v>150649</v>
-      </c>
-      <c r="J13" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K13" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L13" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M13" s="70" t="inlineStr">
-        <is>
-          <t>IncomeTaxExpenseBenefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B14" s="70" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="C14" s="70" t="inlineStr">
-        <is>
-          <t>3S!row36/62</t>
-        </is>
-      </c>
-      <c r="D14" s="70" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="E14" s="70" t="inlineStr">
-        <is>
-          <t>Same naming.</t>
-        </is>
-      </c>
-      <c r="F14" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income / Cash Flows</t>
-        </is>
-      </c>
-      <c r="G14" s="70" t="n">
-        <v>429375</v>
-      </c>
-      <c r="H14" s="70" t="n">
-        <v>512811</v>
-      </c>
-      <c r="I14" s="70" t="n">
-        <v>651946</v>
-      </c>
-      <c r="J14" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K14" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L14" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M14" s="70" t="inlineStr">
-        <is>
-          <t>NetIncomeLoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B15" s="70" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C15" s="70" t="inlineStr">
-        <is>
-          <t>3S!row30/63; DCF!E23</t>
-        </is>
-      </c>
-      <c r="D15" s="70" t="inlineStr">
-        <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="E15" s="70" t="inlineStr">
-        <is>
-          <t>From Consolidated Statements of Cash Flows (add-back).</t>
-        </is>
-      </c>
-      <c r="F15" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Cash Flows</t>
-        </is>
-      </c>
-      <c r="G15" s="70" t="n">
-        <v>14638</v>
-      </c>
-      <c r="H15" s="70" t="n">
-        <v>13827</v>
-      </c>
-      <c r="I15" s="70" t="n">
-        <v>14952</v>
-      </c>
-      <c r="J15" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K15" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L15" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M15" s="70" t="inlineStr">
-        <is>
-          <t>DepreciationDepletionAndAmortization</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B16" s="70" t="inlineStr">
-        <is>
-          <t>CapEx</t>
-        </is>
-      </c>
-      <c r="C16" s="70" t="inlineStr">
-        <is>
-          <t>3S!row68; DCF!D15 / row24</t>
-        </is>
-      </c>
-      <c r="D16" s="70" t="inlineStr">
-        <is>
-          <t>Purchases of property and equipment + Capitalized internal-use software costs</t>
-        </is>
-      </c>
-      <c r="E16" s="70" t="inlineStr">
-        <is>
-          <t>NAMING / SCOPE. CFI 'Investments in Property &amp; Equipment' / DCF Capex. FICO CapEx for modeling = PPE purchases + capitalized internal-use software (both in CF investing). FY25: 8,922 + 30,485 = 39,407.</t>
-        </is>
-      </c>
-      <c r="F16" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Cash Flows — Investing activities</t>
-        </is>
-      </c>
-      <c r="G16" s="70" t="n">
-        <v>4237</v>
-      </c>
-      <c r="H16" s="70" t="n">
-        <v>25551</v>
-      </c>
-      <c r="I16" s="70" t="n">
-        <v>39407</v>
-      </c>
-      <c r="J16" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K16" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L16" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M16" s="70" t="inlineStr">
-        <is>
-          <t>PaymentsToAcquirePPE + Capitalized internal-use software (10-K CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B17" s="70" t="inlineStr">
-        <is>
-          <t>Changes in NWC</t>
-        </is>
-      </c>
-      <c r="C17" s="70" t="inlineStr">
-        <is>
-          <t>3S!row64; DCF!E25</t>
-        </is>
-      </c>
-      <c r="D17" s="70" t="inlineStr">
-        <is>
-          <t>Derived Δ(Accounts receivable − Accounts payable)</t>
-        </is>
-      </c>
-      <c r="E17" s="70" t="inlineStr">
-        <is>
-          <t>Not a single printed 10-K total. Built from BS: AR and AP. CF also shows AR/AP working-capital lines separately.</t>
-        </is>
-      </c>
-      <c r="F17" s="70" t="inlineStr">
-        <is>
-          <t>Balance Sheet + Cash Flow working capital lines</t>
-        </is>
-      </c>
-      <c r="G17" s="70" t="n">
-        <v>63801</v>
-      </c>
-      <c r="H17" s="70" t="n">
-        <v>35231</v>
-      </c>
-      <c r="I17" s="70" t="n">
-        <v>92664</v>
-      </c>
-      <c r="J17" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K17" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L17" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M17" s="70" t="inlineStr">
-        <is>
-          <t>Derived from AccountsReceivableNetCurrent &amp; AccountsPayableCurrent</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B18" s="70" t="inlineStr">
-        <is>
-          <t>Operating Cash Flow</t>
-        </is>
-      </c>
-      <c r="C18" s="70" t="inlineStr">
-        <is>
-          <t>3S!row65</t>
-        </is>
-      </c>
-      <c r="D18" s="70" t="inlineStr">
-        <is>
-          <t>Net cash provided by operating activities</t>
-        </is>
-      </c>
-      <c r="E18" s="70" t="inlineStr">
-        <is>
-          <t>Same meaning; FICO wording is longer.</t>
-        </is>
-      </c>
-      <c r="F18" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Cash Flows</t>
-        </is>
-      </c>
-      <c r="G18" s="70" t="n">
-        <v>468915</v>
-      </c>
-      <c r="H18" s="70" t="n">
-        <v>632964</v>
-      </c>
-      <c r="I18" s="70" t="n">
-        <v>778807</v>
-      </c>
-      <c r="J18" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K18" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L18" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M18" s="70" t="inlineStr">
-        <is>
-          <t>NetCashProvidedByUsedInOperatingActivities</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B19" s="70" t="inlineStr">
-        <is>
-          <t>Cash &amp; Equivalents</t>
-        </is>
-      </c>
-      <c r="C19" s="70" t="inlineStr">
-        <is>
-          <t>3S!row41; DCF!D14 (overridden by 10-Q bridge)</t>
-        </is>
-      </c>
-      <c r="D19" s="70" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="E19" s="70" t="inlineStr">
-        <is>
-          <t>YE 10-K cash. DCF bridge may use later 10-Q cash + marketable securities.</t>
-        </is>
-      </c>
-      <c r="F19" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G19" s="70" t="n">
-        <v>136778</v>
-      </c>
-      <c r="H19" s="70" t="n">
-        <v>150667</v>
-      </c>
-      <c r="I19" s="70" t="n">
-        <v>134136</v>
-      </c>
-      <c r="J19" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K19" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L19" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M19" s="70" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalentsAtCarryingValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B20" s="70" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C20" s="70" t="inlineStr">
-        <is>
-          <t>3S!row42</t>
-        </is>
-      </c>
-      <c r="D20" s="70" t="inlineStr">
-        <is>
-          <t>Accounts receivable, net</t>
-        </is>
-      </c>
-      <c r="E20" s="70" t="inlineStr">
-        <is>
-          <t>Same; 10-K says ', net'.</t>
-        </is>
-      </c>
-      <c r="F20" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G20" s="70" t="n">
-        <v>387947</v>
-      </c>
-      <c r="H20" s="70" t="n">
-        <v>426642</v>
-      </c>
-      <c r="I20" s="70" t="n">
-        <v>529148</v>
-      </c>
-      <c r="J20" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K20" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L20" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M20" s="70" t="inlineStr">
-        <is>
-          <t>AccountsReceivableNetCurrent</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B21" s="70" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="C21" s="70" t="inlineStr">
-        <is>
-          <t>3S!row43</t>
-        </is>
-      </c>
-      <c r="D21" s="70" t="inlineStr">
-        <is>
-          <t>(not material / not presented)</t>
-        </is>
-      </c>
-      <c r="E21" s="70" t="inlineStr">
-        <is>
-          <t>FICO software/scores business — no material inventory line; model uses 0.</t>
-        </is>
-      </c>
-      <c r="F21" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G21" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K21" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L21" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M21" s="70" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B22" s="70" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="C22" s="70" t="inlineStr">
-        <is>
-          <t>not a CFI hard input (informational)</t>
-        </is>
-      </c>
-      <c r="D22" s="70" t="inlineStr">
-        <is>
-          <t>Total current assets</t>
-        </is>
-      </c>
-      <c r="E22" s="70" t="inlineStr">
-        <is>
-          <t>From 10-K balance sheet total current assets.</t>
-        </is>
-      </c>
-      <c r="F22" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G22" s="70" t="n">
-        <v>556448</v>
-      </c>
-      <c r="H22" s="70" t="n">
-        <v>617413</v>
-      </c>
-      <c r="I22" s="70" t="n">
-        <v>705165</v>
-      </c>
-      <c r="J22" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K22" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L22" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M22" s="70" t="inlineStr">
-        <is>
-          <t>AssetsCurrent</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B23" s="70" t="inlineStr">
-        <is>
-          <t>Net PP&amp;E</t>
-        </is>
-      </c>
-      <c r="C23" s="70" t="inlineStr">
-        <is>
-          <t>3S!row44</t>
-        </is>
-      </c>
-      <c r="D23" s="70" t="inlineStr">
-        <is>
-          <t>Property and equipment, net</t>
-        </is>
-      </c>
-      <c r="E23" s="70" t="inlineStr">
-        <is>
-          <t>Same meaning.</t>
-        </is>
-      </c>
-      <c r="F23" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G23" s="70" t="n">
-        <v>10966</v>
-      </c>
-      <c r="H23" s="70" t="n">
-        <v>38465</v>
-      </c>
-      <c r="I23" s="70" t="n">
-        <v>67713</v>
-      </c>
-      <c r="J23" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K23" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L23" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M23" s="70" t="inlineStr">
-        <is>
-          <t>PropertyPlantAndEquipmentNet</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B24" s="70" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="C24" s="70" t="inlineStr">
-        <is>
-          <t>3S!row45 (formula in template)</t>
-        </is>
-      </c>
-      <c r="D24" s="70" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="E24" s="70" t="inlineStr">
-        <is>
-          <t>SEC total assets provided for reference; CFI row 45 is a SUM formula — do not overwrite.</t>
-        </is>
-      </c>
-      <c r="F24" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G24" s="70" t="n">
-        <v>1575281</v>
-      </c>
-      <c r="H24" s="70" t="n">
-        <v>1717884</v>
-      </c>
-      <c r="I24" s="70" t="n">
-        <v>1868133</v>
-      </c>
-      <c r="J24" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K24" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L24" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M24" s="70" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B25" s="70" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C25" s="70" t="inlineStr">
-        <is>
-          <t>3S!row48</t>
-        </is>
-      </c>
-      <c r="D25" s="70" t="inlineStr">
-        <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="E25" s="70" t="inlineStr">
-        <is>
-          <t>Same naming.</t>
-        </is>
-      </c>
-      <c r="F25" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G25" s="70" t="n">
-        <v>19009</v>
-      </c>
-      <c r="H25" s="70" t="n">
-        <v>22473</v>
-      </c>
-      <c r="I25" s="70" t="n">
-        <v>32315</v>
-      </c>
-      <c r="J25" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K25" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L25" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M25" s="70" t="inlineStr">
-        <is>
-          <t>AccountsPayableCurrent</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B26" s="70" t="inlineStr">
-        <is>
-          <t>Total Debt</t>
-        </is>
-      </c>
-      <c r="C26" s="70" t="inlineStr">
-        <is>
-          <t>3S!row49; DCF!D13 (10-Q override optional)</t>
-        </is>
-      </c>
-      <c r="D26" s="70" t="inlineStr">
-        <is>
-          <t>Current maturities of long-term debt + Long-term debt</t>
-        </is>
-      </c>
-      <c r="E26" s="70" t="inlineStr">
-        <is>
-          <t>Sum of current + noncurrent debt from BS / debt footnote. FY25 total debt 3,055,691. DCF may override D13 with later 10-Q debt.</t>
-        </is>
-      </c>
-      <c r="F26" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets / Debt footnote</t>
-        </is>
-      </c>
-      <c r="G26" s="70" t="n">
-        <v>1811658</v>
-      </c>
-      <c r="H26" s="70" t="n">
-        <v>2209021</v>
-      </c>
-      <c r="I26" s="70" t="n">
-        <v>3055691</v>
-      </c>
-      <c r="J26" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K26" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L26" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M26" s="70" t="inlineStr">
-        <is>
-          <t>LongTermDebtCurrent + LongTermDebtNoncurrent / 10-K note</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B27" s="70" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
-        </is>
-      </c>
-      <c r="C27" s="70" t="inlineStr">
-        <is>
-          <t>3S!row53</t>
-        </is>
-      </c>
-      <c r="D27" s="70" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="E27" s="70" t="inlineStr">
-        <is>
-          <t>Same; equity section of balance sheet / equity statement.</t>
-        </is>
-      </c>
-      <c r="F27" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets / Stockholders' equity</t>
-        </is>
-      </c>
-      <c r="G27" s="70" t="n">
-        <v>3388059</v>
-      </c>
-      <c r="H27" s="70" t="n">
-        <v>3900870</v>
-      </c>
-      <c r="I27" s="70" t="n">
-        <v>4552816</v>
-      </c>
-      <c r="J27" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K27" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L27" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M27" s="70" t="inlineStr">
-        <is>
-          <t>RetainedEarningsAccumulatedDeficit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="70" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B28" s="70" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="C28" s="70" t="inlineStr">
-        <is>
-          <t>3S!row54 (formula/total)</t>
-        </is>
-      </c>
-      <c r="D28" s="70" t="inlineStr">
-        <is>
-          <t>Total stockholders' deficit / equity</t>
-        </is>
-      </c>
-      <c r="E28" s="70" t="inlineStr">
-        <is>
-          <t>FICO reports stockholders' deficit (negative equity) due to buybacks.</t>
-        </is>
-      </c>
-      <c r="F28" s="70" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G28" s="70" t="n">
-        <v>-687990</v>
-      </c>
-      <c r="H28" s="70" t="n">
-        <v>-962679</v>
-      </c>
-      <c r="I28" s="70" t="n">
-        <v>-1745784</v>
-      </c>
-      <c r="J28" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K28" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L28" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M28" s="70" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="68" t="inlineStr">
-        <is>
-          <t>FILING INDEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>FY2025 10-K HTML</t>
-        </is>
-      </c>
-      <c r="B32" s="72" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FY2024 10-K HTML</t>
-        </is>
-      </c>
-      <c r="B33" s="72" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>FY2023 10-K HTML</t>
-        </is>
-      </c>
-      <c r="B34" s="72" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SEC companyfacts API</t>
-        </is>
-      </c>
-      <c r="B35" s="72" t="inlineStr">
-        <is>
-          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>10-Q browse (debt/cash bridge)</t>
-        </is>
-      </c>
-      <c r="B36" s="72" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0000814547&amp;type=10-Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="68" t="inlineStr">
-        <is>
-          <t>DCF bridge overrides (not YE 10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>DCF!D13 Debt (10-Q)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>5582389</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Later interim debt; override YE 10-K if bridging to current EV</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>DCF!D14 Cash (10-Q cash+mkt secs)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>304537</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Cash &amp; cash equivalents + marketable securities from latest 10-Q bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>DCF!D11 Price / D12 Shares</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1046.23 / 21597.635</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Market price &amp; diluted shares (000s) — not from 10-K income statement</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operating income (projected from FY25 base)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2956,7 +1120,7 @@
       <c r="B12" s="50" t="n"/>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>FICO — DCF Model (CFI template + 10-K sourced inputs)</t>
+          <t>FICO — DCF Model (complete values + chart)</t>
         </is>
       </c>
       <c r="D12" s="50" t="n"/>
@@ -3104,7 +1268,7 @@
       <c r="B20" s="50" t="n"/>
       <c r="C20" s="56" t="inlineStr">
         <is>
-          <t>Open 10K_Sources first — every number has a 10-K URL and naming note.</t>
+          <t>This Excel model is for educational purposes only and should not be used for any other reason.</t>
         </is>
       </c>
       <c r="D20" s="56" t="n"/>
@@ -3323,19 +1487,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.08984375" defaultRowHeight="15.5"/>
   <cols>
     <col width="3.54296875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="28" customWidth="1" style="1" min="2" max="2"/>
-    <col width="24" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16" customWidth="1" style="2" min="4" max="4"/>
-    <col width="16" customWidth="1" style="1" min="5" max="9"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" style="1" min="10" max="14"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.453125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="14" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14" customWidth="1" style="1" min="5" max="9"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="1" min="10" max="14"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="9.08984375" customWidth="1" style="1" min="15" max="16384"/>
   </cols>
   <sheetData>
@@ -3363,13 +1527,13 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>FICO DCF Model</t>
+          <t>FICO DCF Model (values filled)</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
-      <c r="D2" s="73" t="inlineStr">
-        <is>
-          <t>See 10K_Sources for every input link</t>
+      <c r="D2" s="69" t="inlineStr">
+        <is>
+          <t>All DCF lines filled — open 10K_Sources for SEC links</t>
         </is>
       </c>
       <c r="E2" s="7" t="n"/>
@@ -3429,7 +1593,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="n"/>
-      <c r="D5" s="74" t="n">
+      <c r="D5" s="70" t="n">
         <v>0.1877</v>
       </c>
       <c r="E5" s="21" t="n"/>
@@ -3452,7 +1616,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n"/>
-      <c r="D6" s="74" t="n">
+      <c r="D6" s="71" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="23" t="n"/>
@@ -3475,7 +1639,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n"/>
-      <c r="D7" s="74" t="n">
+      <c r="D7" s="71" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="23" t="n"/>
@@ -3498,7 +1662,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n"/>
-      <c r="D8" s="75" t="n">
+      <c r="D8" s="72" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="23" t="n"/>
@@ -3521,7 +1685,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n"/>
-      <c r="D9" s="76" t="n">
+      <c r="D9" s="73" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="23" t="n"/>
@@ -3544,7 +1708,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n"/>
-      <c r="D10" s="76" t="n">
+      <c r="D10" s="73" t="n">
         <v>45930</v>
       </c>
       <c r="E10" s="23" t="n"/>
@@ -3567,7 +1731,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n"/>
-      <c r="D11" s="77" t="n">
+      <c r="D11" s="74" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="23" t="n"/>
@@ -3590,7 +1754,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n"/>
-      <c r="D12" s="78" t="n">
+      <c r="D12" s="75" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="23" t="n"/>
@@ -3613,7 +1777,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n"/>
-      <c r="D13" s="78" t="n">
+      <c r="D13" s="76" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="23" t="n"/>
@@ -3636,7 +1800,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n"/>
-      <c r="D14" s="78" t="n">
+      <c r="D14" s="76" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="23" t="n"/>
@@ -3659,7 +1823,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n"/>
-      <c r="D15" s="79" t="n">
+      <c r="D15" s="77" t="n">
         <v>39407</v>
       </c>
       <c r="E15" s="23" t="n"/>
@@ -3699,25 +1863,20 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="45">
-        <f>YEAR(E18)</f>
-        <v/>
-      </c>
-      <c r="F17" s="45">
-        <f>YEAR(F18)</f>
-        <v/>
-      </c>
-      <c r="G17" s="45">
-        <f>YEAR(G18)</f>
-        <v/>
-      </c>
-      <c r="H17" s="45">
-        <f>YEAR(H18)</f>
-        <v/>
-      </c>
-      <c r="I17" s="45">
-        <f>YEAR(I18)</f>
-        <v/>
+      <c r="E17" s="78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F17" s="78" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G17" s="78" t="n">
+        <v>2028</v>
+      </c>
+      <c r="H17" s="78" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I17" s="78" t="n">
+        <v>2030</v>
       </c>
       <c r="J17" s="44" t="inlineStr">
         <is>
@@ -3742,44 +1901,36 @@
         </is>
       </c>
       <c r="C18" s="23" t="n"/>
-      <c r="D18" s="37">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="E18" s="37">
-        <f>DATE(YEAR($D$10)+E19,9,30)</f>
-        <v/>
-      </c>
-      <c r="F18" s="37">
-        <f>DATE(YEAR($D$10)+F19,9,30)</f>
-        <v/>
-      </c>
-      <c r="G18" s="37">
-        <f>DATE(YEAR($D$10)+G19,9,30)</f>
-        <v/>
-      </c>
-      <c r="H18" s="37">
-        <f>DATE(YEAR($D$10)+H19,9,30)</f>
-        <v/>
-      </c>
-      <c r="I18" s="37">
-        <f>DATE(YEAR($D$10)+I19,9,30)</f>
-        <v/>
-      </c>
-      <c r="J18" s="41">
-        <f>I18</f>
-        <v/>
+      <c r="D18" s="79" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E18" s="79" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" s="79" t="n">
+        <v>46660</v>
+      </c>
+      <c r="G18" s="79" t="n">
+        <v>47026</v>
+      </c>
+      <c r="H18" s="79" t="n">
+        <v>47391</v>
+      </c>
+      <c r="I18" s="79" t="n">
+        <v>47756</v>
+      </c>
+      <c r="J18" s="80" t="n">
+        <v>47756</v>
       </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t>Perpetural Growth</t>
+          <t>Perpetual Growth</t>
         </is>
       </c>
       <c r="M18" s="23" t="n"/>
-      <c r="N18" s="23">
-        <f>(I26*(1+D7))/(D6-D7)</f>
-        <v/>
+      <c r="N18" s="81" t="n">
+        <v>23982690.1</v>
       </c>
       <c r="O18" s="23" t="n"/>
     </row>
@@ -3792,24 +1943,20 @@
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="37" t="n"/>
-      <c r="E19" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="39">
-        <f>E19+1</f>
-        <v/>
-      </c>
-      <c r="G19" s="39">
-        <f>F19+1</f>
-        <v/>
-      </c>
-      <c r="H19" s="39">
-        <f>G19+1</f>
-        <v/>
-      </c>
-      <c r="I19" s="39">
-        <f>H19+1</f>
-        <v/>
+      <c r="E19" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="83" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="83" t="n">
+        <v>5</v>
       </c>
       <c r="J19" s="37" t="n"/>
       <c r="K19" s="23" t="n"/>
@@ -3819,9 +1966,8 @@
         </is>
       </c>
       <c r="M19" s="23" t="n"/>
-      <c r="N19" s="80">
-        <f>D8*(I21+I23)</f>
-        <v/>
+      <c r="N19" s="81" t="n">
+        <v>48732457.5</v>
       </c>
       <c r="O19" s="23" t="n"/>
     </row>
@@ -3834,25 +1980,20 @@
       </c>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="23" t="n"/>
-      <c r="E20" s="81">
-        <f>YEARFRAC(D18,E18)</f>
-        <v/>
-      </c>
-      <c r="F20" s="81">
-        <f>YEARFRAC(E18,F18)</f>
-        <v/>
-      </c>
-      <c r="G20" s="81">
-        <f>YEARFRAC(F18,G18)</f>
-        <v/>
-      </c>
-      <c r="H20" s="81">
-        <f>YEARFRAC(G18,H18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="81">
-        <f>YEARFRAC(H18,I18)</f>
-        <v/>
+      <c r="E20" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="84" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="H20" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="84" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="23" t="n"/>
@@ -3862,9 +2003,8 @@
         </is>
       </c>
       <c r="M20" s="23" t="n"/>
-      <c r="N20" s="18">
-        <f>AVERAGE(N18:N19)</f>
-        <v/>
+      <c r="N20" s="85" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="O20" s="23" t="n"/>
     </row>
@@ -3877,19 +2017,19 @@
       </c>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
-      <c r="E21" s="79" t="n">
+      <c r="E21" s="77" t="n">
         <v>1048623.4</v>
       </c>
-      <c r="F21" s="79" t="n">
+      <c r="F21" s="77" t="n">
         <v>1284433.8</v>
       </c>
-      <c r="G21" s="79" t="n">
+      <c r="G21" s="77" t="n">
         <v>1505458.6</v>
       </c>
-      <c r="H21" s="79" t="n">
+      <c r="H21" s="77" t="n">
         <v>1717399.8</v>
       </c>
-      <c r="I21" s="79" t="n">
+      <c r="I21" s="77" t="n">
         <v>1922965.4</v>
       </c>
       <c r="J21" s="23" t="n"/>
@@ -3908,25 +2048,20 @@
       </c>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="80">
-        <f>E21*$D$5</f>
-        <v/>
-      </c>
-      <c r="F22" s="80">
-        <f>F21*$D$5</f>
-        <v/>
-      </c>
-      <c r="G22" s="80">
-        <f>G21*$D$5</f>
-        <v/>
-      </c>
-      <c r="H22" s="80">
-        <f>H21*$D$5</f>
-        <v/>
-      </c>
-      <c r="I22" s="80">
-        <f>I21*$D$5</f>
-        <v/>
+      <c r="E22" s="81" t="n">
+        <v>196829.1</v>
+      </c>
+      <c r="F22" s="81" t="n">
+        <v>241091.3</v>
+      </c>
+      <c r="G22" s="81" t="n">
+        <v>282578.2</v>
+      </c>
+      <c r="H22" s="81" t="n">
+        <v>322360</v>
+      </c>
+      <c r="I22" s="81" t="n">
+        <v>360945.2</v>
       </c>
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
@@ -3944,19 +2079,19 @@
       </c>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="82" t="n">
+      <c r="E23" s="77" t="n">
         <v>18156.7</v>
       </c>
-      <c r="F23" s="82" t="n">
+      <c r="F23" s="77" t="n">
         <v>20335.5</v>
       </c>
-      <c r="G23" s="82" t="n">
+      <c r="G23" s="77" t="n">
         <v>22369.1</v>
       </c>
-      <c r="H23" s="82" t="n">
+      <c r="H23" s="77" t="n">
         <v>24382.3</v>
       </c>
-      <c r="I23" s="82" t="n">
+      <c r="I23" s="77" t="n">
         <v>26332.9</v>
       </c>
       <c r="J23" s="23" t="n"/>
@@ -3975,25 +2110,20 @@
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="29">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="F24" s="29">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="G24" s="29">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="H24" s="29">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="I24" s="29">
-        <f>$D$15</f>
-        <v/>
+      <c r="E24" s="86" t="n">
+        <v>39407</v>
+      </c>
+      <c r="F24" s="86" t="n">
+        <v>39407</v>
+      </c>
+      <c r="G24" s="86" t="n">
+        <v>39407</v>
+      </c>
+      <c r="H24" s="86" t="n">
+        <v>39407</v>
+      </c>
+      <c r="I24" s="86" t="n">
+        <v>39407</v>
       </c>
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
@@ -4011,19 +2141,19 @@
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="79" t="n">
+      <c r="E25" s="77" t="n">
         <v>13936.1</v>
       </c>
-      <c r="F25" s="79" t="n">
+      <c r="F25" s="77" t="n">
         <v>13617.5</v>
       </c>
-      <c r="G25" s="79" t="n">
+      <c r="G25" s="77" t="n">
         <v>12709.7</v>
       </c>
-      <c r="H25" s="79" t="n">
+      <c r="H25" s="77" t="n">
         <v>12582.6</v>
       </c>
-      <c r="I25" s="79" t="n">
+      <c r="I25" s="77" t="n">
         <v>12191.2</v>
       </c>
       <c r="J25" s="23" t="n"/>
@@ -4042,25 +2172,20 @@
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="18">
-        <f>E21-E22+E23-E24-E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="18">
-        <f>F21-F22+F23-F24-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="18">
-        <f>G21-G22+G23-G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="18">
-        <f>H21-H22+H23-H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="18">
-        <f>I21-I22+I23-I24-I25</f>
-        <v/>
+      <c r="E26" s="85" t="n">
+        <v>816607.9</v>
+      </c>
+      <c r="F26" s="85" t="n">
+        <v>1010653.5</v>
+      </c>
+      <c r="G26" s="85" t="n">
+        <v>1193132.8</v>
+      </c>
+      <c r="H26" s="85" t="n">
+        <v>1367432.5</v>
+      </c>
+      <c r="I26" s="85" t="n">
+        <v>1536754.9</v>
       </c>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
@@ -4077,18 +2202,16 @@
         </is>
       </c>
       <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23">
-        <f>-I35</f>
-        <v/>
+      <c r="D27" s="81" t="n">
+        <v>-27873945.7</v>
       </c>
       <c r="E27" s="23" t="n"/>
       <c r="F27" s="23" t="n"/>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="23" t="n"/>
       <c r="I27" s="23" t="n"/>
-      <c r="J27" s="23">
-        <f>N20</f>
-        <v/>
+      <c r="J27" s="81" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
@@ -4104,32 +2227,26 @@
         </is>
       </c>
       <c r="C28" s="23" t="n"/>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="18">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H28" s="18">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J28" s="18">
-        <f>J27+J26</f>
-        <v/>
+      <c r="E28" s="85" t="n">
+        <v>816607.9</v>
+      </c>
+      <c r="F28" s="85" t="n">
+        <v>1010653.5</v>
+      </c>
+      <c r="G28" s="85" t="n">
+        <v>1196401.7</v>
+      </c>
+      <c r="H28" s="85" t="n">
+        <v>1367432.5</v>
+      </c>
+      <c r="I28" s="85" t="n">
+        <v>1536754.9</v>
+      </c>
+      <c r="J28" s="85" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -4145,33 +2262,26 @@
         </is>
       </c>
       <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23">
-        <f>D27+D26</f>
-        <v/>
-      </c>
-      <c r="E29" s="23">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F29" s="23">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G29" s="23">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H29" s="23">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I29" s="23">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J29" s="23">
-        <f>J27</f>
-        <v/>
+      <c r="D29" s="81" t="n">
+        <v>-27873945.7</v>
+      </c>
+      <c r="E29" s="81" t="n">
+        <v>816607.9</v>
+      </c>
+      <c r="F29" s="81" t="n">
+        <v>1010653.5</v>
+      </c>
+      <c r="G29" s="81" t="n">
+        <v>1196401.7</v>
+      </c>
+      <c r="H29" s="81" t="n">
+        <v>1367432.5</v>
+      </c>
+      <c r="I29" s="81" t="n">
+        <v>1536754.9</v>
+      </c>
+      <c r="J29" s="81" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
@@ -4229,9 +2339,8 @@
         </is>
       </c>
       <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23">
-        <f>XNPV(D6,D28:J28,D18:J18)</f>
-        <v/>
+      <c r="D32" s="81" t="n">
+        <v>27395820.3</v>
       </c>
       <c r="E32" s="23" t="n"/>
       <c r="G32" s="23" t="inlineStr">
@@ -4240,9 +2349,8 @@
         </is>
       </c>
       <c r="H32" s="23" t="n"/>
-      <c r="I32" s="23">
-        <f>D12*D11</f>
-        <v/>
+      <c r="I32" s="81" t="n">
+        <v>22596093.7</v>
       </c>
       <c r="J32" s="23" t="n"/>
       <c r="L32" s="23" t="inlineStr">
@@ -4251,9 +2359,8 @@
         </is>
       </c>
       <c r="M32" s="23" t="n"/>
-      <c r="N32" s="46">
-        <f>D37/I37-1</f>
-        <v/>
+      <c r="N32" s="87" t="n">
+        <v>-0.0212</v>
       </c>
       <c r="O32" s="23" t="n"/>
     </row>
@@ -4265,9 +2372,8 @@
         </is>
       </c>
       <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23">
-        <f>+D14</f>
-        <v/>
+      <c r="D33" s="81" t="n">
+        <v>304537</v>
       </c>
       <c r="E33" s="23" t="n"/>
       <c r="G33" s="23" t="inlineStr">
@@ -4276,9 +2382,8 @@
         </is>
       </c>
       <c r="H33" s="23" t="n"/>
-      <c r="I33" s="23">
-        <f>D13</f>
-        <v/>
+      <c r="I33" s="81" t="n">
+        <v>5582389</v>
       </c>
       <c r="J33" s="23" t="n"/>
       <c r="L33" s="23" t="inlineStr">
@@ -4287,9 +2392,8 @@
         </is>
       </c>
       <c r="M33" s="23" t="n"/>
-      <c r="N33" s="46">
-        <f>XIRR(D29:J29,D18:J18)</f>
-        <v/>
+      <c r="N33" s="87" t="n">
+        <v>0.092</v>
       </c>
       <c r="O33" s="23" t="n"/>
     </row>
@@ -4301,9 +2405,8 @@
         </is>
       </c>
       <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23">
-        <f>+D13</f>
-        <v/>
+      <c r="D34" s="81" t="n">
+        <v>5582389</v>
       </c>
       <c r="E34" s="23" t="n"/>
       <c r="G34" s="23" t="inlineStr">
@@ -4312,9 +2415,8 @@
         </is>
       </c>
       <c r="H34" s="23" t="n"/>
-      <c r="I34" s="23">
-        <f>+D14</f>
-        <v/>
+      <c r="I34" s="81" t="n">
+        <v>304537</v>
       </c>
       <c r="J34" s="23" t="n"/>
       <c r="L34" s="23" t="n"/>
@@ -4330,9 +2432,8 @@
         </is>
       </c>
       <c r="C35" s="23" t="n"/>
-      <c r="D35" s="18">
-        <f>D32+D33-D34</f>
-        <v/>
+      <c r="D35" s="85" t="n">
+        <v>22117968.3</v>
       </c>
       <c r="E35" s="23" t="n"/>
       <c r="G35" s="23" t="inlineStr">
@@ -4341,9 +2442,8 @@
         </is>
       </c>
       <c r="H35" s="23" t="n"/>
-      <c r="I35" s="18">
-        <f>I32+I33-I34</f>
-        <v/>
+      <c r="I35" s="85" t="n">
+        <v>27873945.7</v>
       </c>
       <c r="J35" s="23" t="n"/>
       <c r="L35" s="42" t="inlineStr">
@@ -4363,7 +2463,7 @@
       <c r="E36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="23" t="n"/>
-      <c r="I36" s="83" t="n"/>
+      <c r="I36" s="88" t="n"/>
       <c r="J36" s="23" t="n"/>
       <c r="L36" s="23" t="inlineStr">
         <is>
@@ -4371,9 +2471,8 @@
         </is>
       </c>
       <c r="M36" s="23" t="n"/>
-      <c r="N36" s="83">
-        <f>I37</f>
-        <v/>
+      <c r="N36" s="89" t="n">
+        <v>1046.23</v>
       </c>
       <c r="O36" s="23" t="n"/>
     </row>
@@ -4385,9 +2484,8 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="83">
-        <f>D35/D12</f>
-        <v/>
+      <c r="D37" s="89" t="n">
+        <v>1024.09</v>
       </c>
       <c r="E37" s="23" t="n"/>
       <c r="G37" s="23" t="inlineStr">
@@ -4396,9 +2494,8 @@
         </is>
       </c>
       <c r="H37" s="23" t="n"/>
-      <c r="I37" s="83">
-        <f>D11</f>
-        <v/>
+      <c r="I37" s="89" t="n">
+        <v>1046.23</v>
       </c>
       <c r="J37" s="23" t="n"/>
       <c r="L37" s="23" t="inlineStr">
@@ -4407,9 +2504,8 @@
         </is>
       </c>
       <c r="M37" s="23" t="n"/>
-      <c r="N37" s="83">
-        <f>D37-I37</f>
-        <v/>
+      <c r="N37" s="89" t="n">
+        <v>-22.14</v>
       </c>
       <c r="O37" s="23" t="n"/>
     </row>
@@ -4429,9 +2525,8 @@
         </is>
       </c>
       <c r="M38" s="23" t="n"/>
-      <c r="N38" s="83">
-        <f>SUM(N36:N37)</f>
-        <v/>
+      <c r="N38" s="89" t="n">
+        <v>1024.09</v>
       </c>
       <c r="O38" s="23" t="n"/>
     </row>
@@ -4615,9 +2710,9 @@
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="23" t="n"/>
-      <c r="B50" s="84" t="inlineStr">
-        <is>
-          <t>Sources: sheet 10K_Sources (clickable 10-K links). OpEx = SG&amp;A + R&amp;D from 10-K (CFI names differ). Capex D15 = PPE purchases + capitalized software.</t>
+      <c r="B50" s="90" t="inlineStr">
+        <is>
+          <t>Blue/yellow = inputs. Blue-gray = computed (dates, taxes, Capex, UFCF, TV, EV). Capex = 10-K PPE purchases + capitalized software. Tax = FY25 ETR.</t>
         </is>
       </c>
       <c r="C50" s="23" t="n"/>

--- a/FICO/DCF_FICO.xlsx
+++ b/FICO/DCF_FICO.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="685" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="10K_Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Audit_Fixes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cover Page" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DCF Model" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -64,7 +64,7 @@
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="173" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -246,8 +246,18 @@
       <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -288,6 +298,11 @@
         <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -317,7 +332,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -429,6 +444,8 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="right"/>
@@ -450,6 +467,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="14" fontId="9" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="1" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="172" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="172" fontId="17" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -492,7 +514,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Unlevered Free Cash Flow</a:t>
+              <a:t>Unlevered Free Cash Flow (FY2026–2030)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -531,21 +553,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Fiscal year</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -881,71 +888,349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="68" t="inlineStr">
         <is>
-          <t>FICO DCF — 10-K source links</t>
+          <t>Errors found and fixed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FY2025 10-K</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      <c r="A3" s="69" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B3" s="69" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="C3" s="69" t="inlineStr">
+        <is>
+          <t>Fix</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Capex</t>
+          <t>3S forecast COGS%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Purchases of PPE 8,922 + Capitalized internal-use software 30,485 = 39,407</t>
+          <t>Was 37% (CFI sample)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Now 17.77% from FY25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpEx</t>
+          <t>3S forecast SG&amp;A/R&amp;D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SG&amp;A + R&amp;D on income statement (no single OpEx line)</t>
+          <t>Was $25k / $10k</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Now FY25 SG&amp;A/R&amp;D grown with revenue</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>3S forecast tax</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Was 28%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Now 18.77% FY25 ETR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3S AR / Inv days</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Was 18 / 73</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Now ~97 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3S Capex forecast</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Was ~15k sample</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Now from FY25 39,407 growing 8%/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3S year headers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Formulas blank pre-calc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hardcoded 2021–2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DCF Year-1 EBIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Started ~1,048,623 (&gt;FY25 OpInc)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Path anchored to FY25 OpInc 924,850</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DCF D&amp;A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Used ~18k (0.8% rev)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Anchored to FY25 D&amp;A 14,952</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DCF years</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unclear / missing FY25 base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FY25 actuals in row 16; forecast 2026–2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DCF Capex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Flat 39,407</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grows 8%/yr with investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DCF EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25x → huge TV vs PG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Set 22x; still show PG / multiple / average</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DCF blanks</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Taxes/Capex/UFCF/TV formulas blank in viewer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Written as computed values + chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Operating income (projected from FY25 base)</t>
-        </is>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UFCF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1031318</v>
+      </c>
+      <c r="C21" t="n">
+        <v>752304</v>
+      </c>
+      <c r="D21" t="n">
+        <v>42560</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1149880</v>
+      </c>
+      <c r="C22" t="n">
+        <v>850856</v>
+      </c>
+      <c r="D22" t="n">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1270112</v>
+      </c>
+      <c r="C23" t="n">
+        <v>947058</v>
+      </c>
+      <c r="D23" t="n">
+        <v>49641</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1398473</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1050674</v>
+      </c>
+      <c r="D24" t="n">
+        <v>53613</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1533660</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1160650</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57902</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1120,7 +1405,7 @@
       <c r="B12" s="50" t="n"/>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>FICO — DCF Model (complete values + chart)</t>
+          <t>FICO DCF — corrected anchors &amp; filled values</t>
         </is>
       </c>
       <c r="D12" s="50" t="n"/>
@@ -1489,18 +1774,18 @@
     <col width="3.54296875" customWidth="1" style="1" min="1" max="1"/>
     <col width="34" customWidth="1" style="1" min="2" max="2"/>
     <col width="12.453125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="14" customWidth="1" style="2" min="4" max="4"/>
-    <col width="14" customWidth="1" style="1" min="5" max="9"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" style="1" min="10" max="14"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="9.08984375" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="15" customWidth="1" style="2" min="4" max="4"/>
+    <col width="15" customWidth="1" style="1" min="5" max="9"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" style="1" min="10" max="14"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" style="1" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -1527,13 +1812,13 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>FICO DCF Model (values filled)</t>
+          <t>FICO DCF Model (corrected)</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
-      <c r="D2" s="69" t="inlineStr">
-        <is>
-          <t>All DCF lines filled — open 10K_Sources for SEC links</t>
+      <c r="D2" s="71" t="inlineStr">
+        <is>
+          <t>FIXED: EBIT anchored to FY25 OpInc; years 2026–2030; FY25 base in row 16</t>
         </is>
       </c>
       <c r="E2" s="7" t="n"/>
@@ -1593,7 +1878,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="n"/>
-      <c r="D5" s="70" t="n">
+      <c r="D5" s="72" t="n">
         <v>0.1877</v>
       </c>
       <c r="E5" s="21" t="n"/>
@@ -1616,7 +1901,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n"/>
-      <c r="D6" s="71" t="n">
+      <c r="D6" s="73" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="23" t="n"/>
@@ -1639,7 +1924,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n"/>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="73" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="23" t="n"/>
@@ -1662,8 +1947,8 @@
         </is>
       </c>
       <c r="C8" s="23" t="n"/>
-      <c r="D8" s="72" t="n">
-        <v>25</v>
+      <c r="D8" s="74" t="n">
+        <v>22</v>
       </c>
       <c r="E8" s="23" t="n"/>
       <c r="F8" s="23" t="n"/>
@@ -1685,7 +1970,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n"/>
-      <c r="D9" s="73" t="n">
+      <c r="D9" s="75" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="23" t="n"/>
@@ -1708,7 +1993,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n"/>
-      <c r="D10" s="73" t="n">
+      <c r="D10" s="75" t="n">
         <v>45930</v>
       </c>
       <c r="E10" s="23" t="n"/>
@@ -1731,7 +2016,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n"/>
-      <c r="D11" s="74" t="n">
+      <c r="D11" s="76" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="23" t="n"/>
@@ -1754,7 +2039,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n"/>
-      <c r="D12" s="75" t="n">
+      <c r="D12" s="77" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="23" t="n"/>
@@ -1777,7 +2062,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n"/>
-      <c r="D13" s="76" t="n">
+      <c r="D13" s="78" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="23" t="n"/>
@@ -1800,7 +2085,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n"/>
-      <c r="D14" s="76" t="n">
+      <c r="D14" s="78" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="23" t="n"/>
@@ -1823,13 +2108,29 @@
         </is>
       </c>
       <c r="C15" s="23" t="n"/>
-      <c r="D15" s="77" t="n">
+      <c r="D15" s="79" t="n">
         <v>39407</v>
       </c>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="I15" s="23" t="n"/>
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
@@ -1840,9 +2141,29 @@
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="23" t="n"/>
-      <c r="B16" s="23" t="n"/>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>FY2025 actuals (10-K base)</t>
+        </is>
+      </c>
       <c r="C16" s="23" t="n"/>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="80" t="inlineStr">
+        <is>
+          <t>EBIT/DA/Capex/Tax</t>
+        </is>
+      </c>
+      <c r="E16" s="81" t="n">
+        <v>924850</v>
+      </c>
+      <c r="F16" s="81" t="n">
+        <v>14952</v>
+      </c>
+      <c r="G16" s="81" t="n">
+        <v>39407</v>
+      </c>
+      <c r="H16" s="81" t="n">
+        <v>150649</v>
+      </c>
       <c r="J16" s="23" t="n"/>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="23" t="n"/>
@@ -1858,27 +2179,27 @@
         </is>
       </c>
       <c r="C17" s="43" t="n"/>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D17" s="82" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="78" t="n">
+      <c r="E17" s="83" t="n">
         <v>2026</v>
       </c>
-      <c r="F17" s="78" t="n">
+      <c r="F17" s="83" t="n">
         <v>2027</v>
       </c>
-      <c r="G17" s="78" t="n">
+      <c r="G17" s="83" t="n">
         <v>2028</v>
       </c>
-      <c r="H17" s="78" t="n">
+      <c r="H17" s="83" t="n">
         <v>2029</v>
       </c>
-      <c r="I17" s="78" t="n">
+      <c r="I17" s="83" t="n">
         <v>2030</v>
       </c>
-      <c r="J17" s="44" t="inlineStr">
+      <c r="J17" s="82" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -1901,25 +2222,25 @@
         </is>
       </c>
       <c r="C18" s="23" t="n"/>
-      <c r="D18" s="79" t="n">
+      <c r="D18" s="84" t="n">
         <v>45930</v>
       </c>
-      <c r="E18" s="79" t="n">
+      <c r="E18" s="84" t="n">
         <v>46295</v>
       </c>
-      <c r="F18" s="79" t="n">
+      <c r="F18" s="84" t="n">
         <v>46660</v>
       </c>
-      <c r="G18" s="79" t="n">
+      <c r="G18" s="84" t="n">
         <v>47026</v>
       </c>
-      <c r="H18" s="79" t="n">
+      <c r="H18" s="84" t="n">
         <v>47391</v>
       </c>
-      <c r="I18" s="79" t="n">
+      <c r="I18" s="84" t="n">
         <v>47756</v>
       </c>
-      <c r="J18" s="80" t="n">
+      <c r="J18" s="85" t="n">
         <v>47756</v>
       </c>
       <c r="K18" s="23" t="n"/>
@@ -1929,8 +2250,8 @@
         </is>
       </c>
       <c r="M18" s="23" t="n"/>
-      <c r="N18" s="81" t="n">
-        <v>23982690.1</v>
+      <c r="N18" s="86" t="n">
+        <v>18113172.1</v>
       </c>
       <c r="O18" s="23" t="n"/>
     </row>
@@ -1943,19 +2264,19 @@
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="37" t="n"/>
-      <c r="E19" s="82" t="n">
+      <c r="E19" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="83" t="n">
+      <c r="F19" s="88" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="83" t="n">
+      <c r="G19" s="88" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="83" t="n">
+      <c r="H19" s="88" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="83" t="n">
+      <c r="I19" s="88" t="n">
         <v>5</v>
       </c>
       <c r="J19" s="37" t="n"/>
@@ -1966,8 +2287,8 @@
         </is>
       </c>
       <c r="M19" s="23" t="n"/>
-      <c r="N19" s="81" t="n">
-        <v>48732457.5</v>
+      <c r="N19" s="86" t="n">
+        <v>34250977</v>
       </c>
       <c r="O19" s="23" t="n"/>
     </row>
@@ -1980,19 +2301,19 @@
       </c>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="23" t="n"/>
-      <c r="E20" s="84" t="n">
+      <c r="E20" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="84" t="n">
+      <c r="F20" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="84" t="n">
+      <c r="G20" s="89" t="n">
         <v>1.0027</v>
       </c>
-      <c r="H20" s="84" t="n">
+      <c r="H20" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="84" t="n">
+      <c r="I20" s="89" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="23" t="n"/>
@@ -2003,8 +2324,8 @@
         </is>
       </c>
       <c r="M20" s="23" t="n"/>
-      <c r="N20" s="85" t="n">
-        <v>36357573.8</v>
+      <c r="N20" s="90" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="O20" s="23" t="n"/>
     </row>
@@ -2012,25 +2333,25 @@
       <c r="A21" s="23" t="n"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>EBIT (= Operating income path)</t>
         </is>
       </c>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
-      <c r="E21" s="77" t="n">
-        <v>1048623.4</v>
-      </c>
-      <c r="F21" s="77" t="n">
-        <v>1284433.8</v>
-      </c>
-      <c r="G21" s="77" t="n">
-        <v>1505458.6</v>
-      </c>
-      <c r="H21" s="77" t="n">
-        <v>1717399.8</v>
-      </c>
-      <c r="I21" s="77" t="n">
-        <v>1922965.4</v>
+      <c r="E21" s="79" t="n">
+        <v>1031318.4</v>
+      </c>
+      <c r="F21" s="79" t="n">
+        <v>1149880.5</v>
+      </c>
+      <c r="G21" s="79" t="n">
+        <v>1270112.3</v>
+      </c>
+      <c r="H21" s="79" t="n">
+        <v>1398473.3</v>
+      </c>
+      <c r="I21" s="79" t="n">
+        <v>1533659.6</v>
       </c>
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
@@ -2048,20 +2369,20 @@
       </c>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="81" t="n">
-        <v>196829.1</v>
-      </c>
-      <c r="F22" s="81" t="n">
-        <v>241091.3</v>
-      </c>
-      <c r="G22" s="81" t="n">
-        <v>282578.2</v>
-      </c>
-      <c r="H22" s="81" t="n">
-        <v>322360</v>
-      </c>
-      <c r="I22" s="81" t="n">
-        <v>360945.2</v>
+      <c r="E22" s="86" t="n">
+        <v>193580.9</v>
+      </c>
+      <c r="F22" s="86" t="n">
+        <v>215835.3</v>
+      </c>
+      <c r="G22" s="86" t="n">
+        <v>238403.1</v>
+      </c>
+      <c r="H22" s="86" t="n">
+        <v>262496.8</v>
+      </c>
+      <c r="I22" s="86" t="n">
+        <v>287871.6</v>
       </c>
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
@@ -2079,20 +2400,20 @@
       </c>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="77" t="n">
-        <v>18156.7</v>
-      </c>
-      <c r="F23" s="77" t="n">
-        <v>20335.5</v>
-      </c>
-      <c r="G23" s="77" t="n">
-        <v>22369.1</v>
-      </c>
-      <c r="H23" s="77" t="n">
-        <v>24382.3</v>
-      </c>
-      <c r="I23" s="77" t="n">
-        <v>26332.9</v>
+      <c r="E23" s="79" t="n">
+        <v>16746.2</v>
+      </c>
+      <c r="F23" s="79" t="n">
+        <v>18420.9</v>
+      </c>
+      <c r="G23" s="79" t="n">
+        <v>20078.7</v>
+      </c>
+      <c r="H23" s="79" t="n">
+        <v>21685</v>
+      </c>
+      <c r="I23" s="79" t="n">
+        <v>23203</v>
       </c>
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="23" t="n"/>
@@ -2105,25 +2426,25 @@
       <c r="A24" s="23" t="n"/>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Less: Capex</t>
+          <t>Less: Capex (grows w/ rev)</t>
         </is>
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="86" t="n">
-        <v>39407</v>
-      </c>
-      <c r="F24" s="86" t="n">
-        <v>39407</v>
-      </c>
-      <c r="G24" s="86" t="n">
-        <v>39407</v>
-      </c>
-      <c r="H24" s="86" t="n">
-        <v>39407</v>
-      </c>
-      <c r="I24" s="86" t="n">
-        <v>39407</v>
+      <c r="E24" s="91" t="n">
+        <v>42559.6</v>
+      </c>
+      <c r="F24" s="91" t="n">
+        <v>45964.3</v>
+      </c>
+      <c r="G24" s="91" t="n">
+        <v>49641.5</v>
+      </c>
+      <c r="H24" s="91" t="n">
+        <v>53612.8</v>
+      </c>
+      <c r="I24" s="91" t="n">
+        <v>57901.8</v>
       </c>
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
@@ -2141,20 +2462,20 @@
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="77" t="n">
-        <v>13936.1</v>
-      </c>
-      <c r="F25" s="77" t="n">
-        <v>13617.5</v>
-      </c>
-      <c r="G25" s="77" t="n">
-        <v>12709.7</v>
-      </c>
-      <c r="H25" s="77" t="n">
-        <v>12582.6</v>
-      </c>
-      <c r="I25" s="77" t="n">
-        <v>12191.2</v>
+      <c r="E25" s="79" t="n">
+        <v>59620</v>
+      </c>
+      <c r="F25" s="79" t="n">
+        <v>55645.3</v>
+      </c>
+      <c r="G25" s="79" t="n">
+        <v>55088.8</v>
+      </c>
+      <c r="H25" s="79" t="n">
+        <v>53375</v>
+      </c>
+      <c r="I25" s="79" t="n">
+        <v>50439.3</v>
       </c>
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
@@ -2172,20 +2493,20 @@
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="85" t="n">
-        <v>816607.9</v>
-      </c>
-      <c r="F26" s="85" t="n">
-        <v>1010653.5</v>
-      </c>
-      <c r="G26" s="85" t="n">
-        <v>1193132.8</v>
-      </c>
-      <c r="H26" s="85" t="n">
-        <v>1367432.5</v>
-      </c>
-      <c r="I26" s="85" t="n">
-        <v>1536754.9</v>
+      <c r="E26" s="90" t="n">
+        <v>752304.2</v>
+      </c>
+      <c r="F26" s="90" t="n">
+        <v>850856.4</v>
+      </c>
+      <c r="G26" s="90" t="n">
+        <v>947057.6</v>
+      </c>
+      <c r="H26" s="90" t="n">
+        <v>1050673.8</v>
+      </c>
+      <c r="I26" s="90" t="n">
+        <v>1160649.9</v>
       </c>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
@@ -2202,7 +2523,7 @@
         </is>
       </c>
       <c r="C27" s="23" t="n"/>
-      <c r="D27" s="81" t="n">
+      <c r="D27" s="86" t="n">
         <v>-27873945.7</v>
       </c>
       <c r="E27" s="23" t="n"/>
@@ -2210,8 +2531,8 @@
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="23" t="n"/>
       <c r="I27" s="23" t="n"/>
-      <c r="J27" s="81" t="n">
-        <v>36357573.8</v>
+      <c r="J27" s="86" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
@@ -2227,26 +2548,26 @@
         </is>
       </c>
       <c r="C28" s="23" t="n"/>
-      <c r="D28" s="85" t="n">
+      <c r="D28" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="85" t="n">
-        <v>816607.9</v>
-      </c>
-      <c r="F28" s="85" t="n">
-        <v>1010653.5</v>
-      </c>
-      <c r="G28" s="85" t="n">
-        <v>1196401.7</v>
-      </c>
-      <c r="H28" s="85" t="n">
-        <v>1367432.5</v>
-      </c>
-      <c r="I28" s="85" t="n">
-        <v>1536754.9</v>
-      </c>
-      <c r="J28" s="85" t="n">
-        <v>36357573.8</v>
+      <c r="E28" s="90" t="n">
+        <v>752304.2</v>
+      </c>
+      <c r="F28" s="90" t="n">
+        <v>850856.4</v>
+      </c>
+      <c r="G28" s="90" t="n">
+        <v>949652.3</v>
+      </c>
+      <c r="H28" s="90" t="n">
+        <v>1050673.8</v>
+      </c>
+      <c r="I28" s="90" t="n">
+        <v>1160649.9</v>
+      </c>
+      <c r="J28" s="90" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -2262,26 +2583,26 @@
         </is>
       </c>
       <c r="C29" s="23" t="n"/>
-      <c r="D29" s="81" t="n">
+      <c r="D29" s="86" t="n">
         <v>-27873945.7</v>
       </c>
-      <c r="E29" s="81" t="n">
-        <v>816607.9</v>
-      </c>
-      <c r="F29" s="81" t="n">
-        <v>1010653.5</v>
-      </c>
-      <c r="G29" s="81" t="n">
-        <v>1196401.7</v>
-      </c>
-      <c r="H29" s="81" t="n">
-        <v>1367432.5</v>
-      </c>
-      <c r="I29" s="81" t="n">
-        <v>1536754.9</v>
-      </c>
-      <c r="J29" s="81" t="n">
-        <v>36357573.8</v>
+      <c r="E29" s="86" t="n">
+        <v>752304.2</v>
+      </c>
+      <c r="F29" s="86" t="n">
+        <v>850856.4</v>
+      </c>
+      <c r="G29" s="86" t="n">
+        <v>949652.3</v>
+      </c>
+      <c r="H29" s="86" t="n">
+        <v>1050673.8</v>
+      </c>
+      <c r="I29" s="86" t="n">
+        <v>1160649.9</v>
+      </c>
+      <c r="J29" s="86" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
@@ -2339,8 +2660,8 @@
         </is>
       </c>
       <c r="C32" s="23" t="n"/>
-      <c r="D32" s="81" t="n">
-        <v>27395820.3</v>
+      <c r="D32" s="86" t="n">
+        <v>20127310.6</v>
       </c>
       <c r="E32" s="23" t="n"/>
       <c r="G32" s="23" t="inlineStr">
@@ -2349,7 +2670,7 @@
         </is>
       </c>
       <c r="H32" s="23" t="n"/>
-      <c r="I32" s="81" t="n">
+      <c r="I32" s="86" t="n">
         <v>22596093.7</v>
       </c>
       <c r="J32" s="23" t="n"/>
@@ -2359,8 +2680,8 @@
         </is>
       </c>
       <c r="M32" s="23" t="n"/>
-      <c r="N32" s="87" t="n">
-        <v>-0.0212</v>
+      <c r="N32" s="92" t="n">
+        <v>-0.3428</v>
       </c>
       <c r="O32" s="23" t="n"/>
     </row>
@@ -2372,7 +2693,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n"/>
-      <c r="D33" s="81" t="n">
+      <c r="D33" s="86" t="n">
         <v>304537</v>
       </c>
       <c r="E33" s="23" t="n"/>
@@ -2382,7 +2703,7 @@
         </is>
       </c>
       <c r="H33" s="23" t="n"/>
-      <c r="I33" s="81" t="n">
+      <c r="I33" s="86" t="n">
         <v>5582389</v>
       </c>
       <c r="J33" s="23" t="n"/>
@@ -2392,8 +2713,8 @@
         </is>
       </c>
       <c r="M33" s="23" t="n"/>
-      <c r="N33" s="87" t="n">
-        <v>0.092</v>
+      <c r="N33" s="92" t="n">
+        <v>0.0224</v>
       </c>
       <c r="O33" s="23" t="n"/>
     </row>
@@ -2405,7 +2726,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n"/>
-      <c r="D34" s="81" t="n">
+      <c r="D34" s="86" t="n">
         <v>5582389</v>
       </c>
       <c r="E34" s="23" t="n"/>
@@ -2415,7 +2736,7 @@
         </is>
       </c>
       <c r="H34" s="23" t="n"/>
-      <c r="I34" s="81" t="n">
+      <c r="I34" s="86" t="n">
         <v>304537</v>
       </c>
       <c r="J34" s="23" t="n"/>
@@ -2432,8 +2753,8 @@
         </is>
       </c>
       <c r="C35" s="23" t="n"/>
-      <c r="D35" s="85" t="n">
-        <v>22117968.3</v>
+      <c r="D35" s="90" t="n">
+        <v>14849458.6</v>
       </c>
       <c r="E35" s="23" t="n"/>
       <c r="G35" s="23" t="inlineStr">
@@ -2442,7 +2763,7 @@
         </is>
       </c>
       <c r="H35" s="23" t="n"/>
-      <c r="I35" s="85" t="n">
+      <c r="I35" s="90" t="n">
         <v>27873945.7</v>
       </c>
       <c r="J35" s="23" t="n"/>
@@ -2463,7 +2784,7 @@
       <c r="E36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="23" t="n"/>
-      <c r="I36" s="88" t="n"/>
+      <c r="I36" s="93" t="n"/>
       <c r="J36" s="23" t="n"/>
       <c r="L36" s="23" t="inlineStr">
         <is>
@@ -2471,7 +2792,7 @@
         </is>
       </c>
       <c r="M36" s="23" t="n"/>
-      <c r="N36" s="89" t="n">
+      <c r="N36" s="94" t="n">
         <v>1046.23</v>
       </c>
       <c r="O36" s="23" t="n"/>
@@ -2484,8 +2805,8 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="89" t="n">
-        <v>1024.09</v>
+      <c r="D37" s="94" t="n">
+        <v>687.55</v>
       </c>
       <c r="E37" s="23" t="n"/>
       <c r="G37" s="23" t="inlineStr">
@@ -2494,7 +2815,7 @@
         </is>
       </c>
       <c r="H37" s="23" t="n"/>
-      <c r="I37" s="89" t="n">
+      <c r="I37" s="94" t="n">
         <v>1046.23</v>
       </c>
       <c r="J37" s="23" t="n"/>
@@ -2504,8 +2825,8 @@
         </is>
       </c>
       <c r="M37" s="23" t="n"/>
-      <c r="N37" s="89" t="n">
-        <v>-22.14</v>
+      <c r="N37" s="94" t="n">
+        <v>-358.68</v>
       </c>
       <c r="O37" s="23" t="n"/>
     </row>
@@ -2525,8 +2846,8 @@
         </is>
       </c>
       <c r="M38" s="23" t="n"/>
-      <c r="N38" s="89" t="n">
-        <v>1024.09</v>
+      <c r="N38" s="94" t="n">
+        <v>687.55</v>
       </c>
       <c r="O38" s="23" t="n"/>
     </row>
@@ -2710,9 +3031,9 @@
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="23" t="n"/>
-      <c r="B50" s="90" t="inlineStr">
-        <is>
-          <t>Blue/yellow = inputs. Blue-gray = computed (dates, taxes, Capex, UFCF, TV, EV). Capex = 10-K PPE purchases + capitalized software. Tax = FY25 ETR.</t>
+      <c r="B50" s="95" t="inlineStr">
+        <is>
+          <t>Base FY25 OpInc=924,850 D&amp;A=14,952 Capex=39,407. WACC=9.6% g=3% EV/EBITDA=22x. Source: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
       <c r="C50" s="23" t="n"/>

--- a/FICO/DCF_FICO.xlsx
+++ b/FICO/DCF_FICO.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="685" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Audit_Fixes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Formula_Map" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cover Page" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DCF Model" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -64,7 +64,7 @@
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="173" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -236,6 +236,10 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
@@ -295,7 +299,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -332,7 +336,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -443,10 +447,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="10" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="right"/>
     </xf>
@@ -466,25 +478,18 @@
     <xf numFmtId="3" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="14" fontId="9" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="172" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="172" fontId="17" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="1" fontId="16" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="1" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="2" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="170" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="172" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +519,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Unlevered Free Cash Flow (FY2026–2030)</a:t>
+              <a:t>Unlevered FCF (formula-driven)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -888,349 +893,554 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="68" t="inlineStr">
         <is>
-          <t>Errors found and fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="69" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B3" s="69" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="C3" s="69" t="inlineStr">
-        <is>
-          <t>Fix</t>
+          <t>Updated math — Excel formula dependencies (not typed results)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yellow cells = inputs. Green/white formula cells = depend on other rows/sheets.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3S forecast COGS%</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Was 37% (CFI sample)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Now 17.77% from FY25</t>
+      <c r="A4" s="69" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="69" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="C4" s="69" t="inlineStr">
+        <is>
+          <t>Excel formula / dependency</t>
+        </is>
+      </c>
+      <c r="D4" s="69" t="inlineStr">
+        <is>
+          <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3S forecast SG&amp;A/R&amp;D</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Was $25k / $10k</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Now FY25 SG&amp;A/R&amp;D grown with revenue</t>
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C5" s="70" t="inlineStr">
+        <is>
+          <t>input (or ='03_Three_Statement'!J13 if joined)</t>
+        </is>
+      </c>
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>FY25 ETR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3S forecast tax</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Was 28%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Now 18.77% FY25 ETR</t>
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
+      <c r="B6" s="70" t="inlineStr">
+        <is>
+          <t>E17:I17</t>
+        </is>
+      </c>
+      <c r="C6" s="70">
+        <f>YEAR(E18) …</f>
+        <v/>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>Depends on date row</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3S AR / Inv days</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Was 18 / 73</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Now ~97 / 0</t>
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>E18:I18</t>
+        </is>
+      </c>
+      <c r="C7" s="70">
+        <f>DATE(YEAR($D$10)+E19,9,30)</f>
+        <v/>
+      </c>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>Depends on FYE + period</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3S Capex forecast</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Was ~15k sample</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Now from FY25 39,407 growing 8%/yr</t>
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>Periods</t>
+        </is>
+      </c>
+      <c r="B8" s="70" t="inlineStr">
+        <is>
+          <t>F19:I19</t>
+        </is>
+      </c>
+      <c r="C8" s="70">
+        <f>E19+1 …</f>
+        <v/>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>Depends on prior period</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3S year headers</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Formulas blank pre-calc</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Hardcoded 2021–2030</t>
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>Year fraction</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>E20:I20</t>
+        </is>
+      </c>
+      <c r="C9" s="70">
+        <f>YEARFRAC(prior_date, date)</f>
+        <v/>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Discount stub</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DCF Year-1 EBIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Started ~1,048,623 (&gt;FY25 OpInc)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Path anchored to FY25 OpInc 924,850</t>
+      <c r="A10" s="70" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>E21:I21</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>Standalone: =$D$3*(1+E4) then rolls; Joined: 3-stmt GP−opex−DA</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>Operating income path</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DCF D&amp;A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Used ~18k (0.8% rev)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Anchored to FY25 D&amp;A 14,952</t>
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>Cash Taxes</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>E22:I22</t>
+        </is>
+      </c>
+      <c r="C11" s="70">
+        <f>E21*$D$5</f>
+        <v/>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Depends on EBIT and tax rate</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DCF years</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Unclear / missing FY25 base</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FY25 actuals in row 16; forecast 2026–2030</t>
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>E23:I23</t>
+        </is>
+      </c>
+      <c r="C12" s="70" t="inlineStr">
+        <is>
+          <t>Standalone: =$E$3*E21/$D$3; Joined: ='03_Three_Statement'!J30</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Depends on EBIT or 3-stmt</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DCF Capex</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Flat 39,407</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Grows 8%/yr with investment</t>
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>E24:I24</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>Standalone: =$D$15*(1+$D$16)^E19; Joined: 3-stmt!J68</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Depends on base capex/growth or 3-stmt</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DCF EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>25x → huge TV vs PG</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Set 22x; still show PG / multiple / average</t>
+      <c r="A14" s="70" t="inlineStr">
+        <is>
+          <t>ΔNWC</t>
+        </is>
+      </c>
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>E25:I25</t>
+        </is>
+      </c>
+      <c r="C14" s="70" t="inlineStr">
+        <is>
+          <t>Standalone: =MAX(0,ΔEBIT)*5%; Joined: 3-stmt!J89</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>WC investment</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DCF blanks</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Taxes/Capex/UFCF/TV formulas blank in viewer</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Written as computed values + chart</t>
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>Unlevered FCF</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>E26:I26</t>
+        </is>
+      </c>
+      <c r="C15" s="70">
+        <f>EBIT − Tax + D&amp;A − Capex − ΔNWC</f>
+        <v/>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>Core FCF identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>TV (PG)</t>
+        </is>
+      </c>
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>N18</t>
+        </is>
+      </c>
+      <c r="C16" s="70">
+        <f>(I26*(1+D7))/(D6-D7)</f>
+        <v/>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>Gordon growth on final UFCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>TV (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>N19</t>
+        </is>
+      </c>
+      <c r="C17" s="70">
+        <f>D8*(I21+I23)</f>
+        <v/>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Exit multiple on final EBITDA</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K</t>
+      <c r="A18" s="70" t="inlineStr">
+        <is>
+          <t>TV Average</t>
         </is>
       </c>
       <c r="B18" s="70" t="inlineStr">
         <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="C18" s="70">
+        <f>AVERAGE(N18:N19)</f>
+        <v/>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>Blended exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>D32</t>
+        </is>
+      </c>
+      <c r="C19" s="70">
+        <f>XNPV(D6,D28:J28,D18:J18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>PV of transaction CFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="70" t="inlineStr">
+        <is>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B20" s="70" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C20" s="70">
+        <f>D32+D33−D34</f>
+        <v/>
+      </c>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>EV + cash − debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>Equity / share</t>
+        </is>
+      </c>
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>D37</t>
+        </is>
+      </c>
+      <c r="C21" s="70">
+        <f>D35/D12</f>
+        <v/>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>Depends on equity &amp; shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="70" t="inlineStr">
+        <is>
+          <t>3S Revenue fcst</t>
+        </is>
+      </c>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>J24</t>
+        </is>
+      </c>
+      <c r="C22" s="70">
+        <f>I24*(1+J7)</f>
+        <v/>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>Grows from prior year</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="70" t="inlineStr">
+        <is>
+          <t>3S COGS fcst</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>J25</t>
+        </is>
+      </c>
+      <c r="C23" s="70">
+        <f>J24*J8</f>
+        <v/>
+      </c>
+      <c r="D23" s="70" t="inlineStr">
+        <is>
+          <t>Depends on revenue &amp; COGS%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="70" t="inlineStr">
+        <is>
+          <t>3S Gross Profit</t>
+        </is>
+      </c>
+      <c r="B24" s="70" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="C24" s="70">
+        <f>J24-J25</f>
+        <v/>
+      </c>
+      <c r="D24" s="70" t="inlineStr">
+        <is>
+          <t>Depends on Rev &amp; COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="70" t="inlineStr">
+        <is>
+          <t>3S SG&amp;A fcst</t>
+        </is>
+      </c>
+      <c r="B25" s="70" t="inlineStr">
+        <is>
+          <t>J28</t>
+        </is>
+      </c>
+      <c r="C25" s="70">
+        <f>J9</f>
+        <v/>
+      </c>
+      <c r="D25" s="70" t="inlineStr">
+        <is>
+          <t>Depends on salaries driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="70" t="inlineStr">
+        <is>
+          <t>3S Capex fcst</t>
+        </is>
+      </c>
+      <c r="B26" s="70" t="inlineStr">
+        <is>
+          <t>J68</t>
+        </is>
+      </c>
+      <c r="C26" s="70">
+        <f>J18</f>
+        <v/>
+      </c>
+      <c r="D26" s="70" t="inlineStr">
+        <is>
+          <t>Depends on capex assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="70" t="inlineStr">
+        <is>
+          <t>3S ΔNWC fcst</t>
+        </is>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>J89</t>
+        </is>
+      </c>
+      <c r="C27" s="70">
+        <f>J88-I88</f>
+        <v/>
+      </c>
+      <c r="D27" s="70" t="inlineStr">
+        <is>
+          <t>Depends on NWC schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="B30" s="71" t="inlineStr">
+        <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>UFCF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1031318</v>
-      </c>
-      <c r="C21" t="n">
-        <v>752304</v>
-      </c>
-      <c r="D21" t="n">
-        <v>42560</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1149880</v>
-      </c>
-      <c r="C22" t="n">
-        <v>850856</v>
-      </c>
-      <c r="D22" t="n">
-        <v>45964</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B23" t="n">
-        <v>1270112</v>
-      </c>
-      <c r="C23" t="n">
-        <v>947058</v>
-      </c>
-      <c r="D23" t="n">
-        <v>49641</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1398473</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1050674</v>
-      </c>
-      <c r="D24" t="n">
-        <v>53613</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B25" t="n">
-        <v>1533660</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1160650</v>
-      </c>
-      <c r="D25" t="n">
-        <v>57902</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1403,10 +1613,9 @@
     </row>
     <row r="12" ht="27" customHeight="1">
       <c r="B12" s="50" t="n"/>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>FICO DCF — corrected anchors &amp; filled values</t>
-        </is>
+      <c r="C12" s="51">
+        <f>'DCF Model'!B2</f>
+        <v/>
       </c>
       <c r="D12" s="50" t="n"/>
       <c r="E12" s="50" t="n"/>
@@ -1772,7 +1981,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.08984375" defaultRowHeight="15.5"/>
   <cols>
     <col width="3.54296875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="34" customWidth="1" style="1" min="2" max="2"/>
+    <col width="36" customWidth="1" style="1" min="2" max="2"/>
     <col width="12.453125" customWidth="1" style="1" min="3" max="3"/>
     <col width="15" customWidth="1" style="2" min="4" max="4"/>
     <col width="15" customWidth="1" style="1" min="5" max="9"/>
@@ -1812,13 +2021,13 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>FICO DCF Model (corrected)</t>
+          <t>FICO DCF (formula-driven)</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
-      <c r="D2" s="71" t="inlineStr">
-        <is>
-          <t>FIXED: EBIT anchored to FY25 OpInc; years 2026–2030; FY25 base in row 16</t>
+      <c r="D2" s="72" t="inlineStr">
+        <is>
+          <t>Yellow=inputs. All taxes/UFCF/TV/EV/dates are Excel formulas.</t>
         </is>
       </c>
       <c r="E2" s="7" t="n"/>
@@ -1834,10 +2043,22 @@
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="23" t="n"/>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="21" t="n"/>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>FY25 OpInc (base)</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>FY25 D&amp;A</t>
+        </is>
+      </c>
+      <c r="D3" s="73" t="n">
+        <v>924850</v>
+      </c>
+      <c r="E3" s="74" t="n">
+        <v>14952</v>
+      </c>
       <c r="F3" s="21" t="n"/>
       <c r="G3" s="21" t="n"/>
       <c r="H3" s="21" t="n"/>
@@ -1853,16 +2074,26 @@
       <c r="A4" s="23" t="n"/>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>EBIT growth (explicit)</t>
         </is>
       </c>
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="33" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="23" t="n"/>
-      <c r="H4" s="23" t="n"/>
-      <c r="I4" s="23" t="n"/>
+      <c r="E4" s="75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F4" s="75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H4" s="75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I4" s="75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="J4" s="23" t="n"/>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="23" t="n"/>
@@ -1878,7 +2109,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="n"/>
-      <c r="D5" s="72" t="n">
+      <c r="D5" s="76" t="n">
         <v>0.1877</v>
       </c>
       <c r="E5" s="21" t="n"/>
@@ -1901,7 +2132,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n"/>
-      <c r="D6" s="73" t="n">
+      <c r="D6" s="77" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="23" t="n"/>
@@ -1924,7 +2155,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n"/>
-      <c r="D7" s="73" t="n">
+      <c r="D7" s="77" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="23" t="n"/>
@@ -1947,7 +2178,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n"/>
-      <c r="D8" s="74" t="n">
+      <c r="D8" s="78" t="n">
         <v>22</v>
       </c>
       <c r="E8" s="23" t="n"/>
@@ -1970,7 +2201,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n"/>
-      <c r="D9" s="75" t="n">
+      <c r="D9" s="79" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="23" t="n"/>
@@ -1993,7 +2224,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n"/>
-      <c r="D10" s="75" t="n">
+      <c r="D10" s="79" t="n">
         <v>45930</v>
       </c>
       <c r="E10" s="23" t="n"/>
@@ -2016,7 +2247,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n"/>
-      <c r="D11" s="76" t="n">
+      <c r="D11" s="80" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="23" t="n"/>
@@ -2039,7 +2270,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n"/>
-      <c r="D12" s="77" t="n">
+      <c r="D12" s="81" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="23" t="n"/>
@@ -2062,7 +2293,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n"/>
-      <c r="D13" s="78" t="n">
+      <c r="D13" s="82" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="23" t="n"/>
@@ -2085,7 +2316,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n"/>
-      <c r="D14" s="78" t="n">
+      <c r="D14" s="82" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="23" t="n"/>
@@ -2108,29 +2339,13 @@
         </is>
       </c>
       <c r="C15" s="23" t="n"/>
-      <c r="D15" s="79" t="n">
+      <c r="D15" s="74" t="n">
         <v>39407</v>
       </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
       <c r="I15" s="23" t="n"/>
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
@@ -2143,26 +2358,12 @@
       <c r="A16" s="23" t="n"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>FY2025 actuals (10-K base)</t>
+          <t>Capex growth</t>
         </is>
       </c>
       <c r="C16" s="23" t="n"/>
-      <c r="D16" s="80" t="inlineStr">
-        <is>
-          <t>EBIT/DA/Capex/Tax</t>
-        </is>
-      </c>
-      <c r="E16" s="81" t="n">
-        <v>924850</v>
-      </c>
-      <c r="F16" s="81" t="n">
-        <v>14952</v>
-      </c>
-      <c r="G16" s="81" t="n">
-        <v>39407</v>
-      </c>
-      <c r="H16" s="81" t="n">
-        <v>150649</v>
+      <c r="D16" s="75" t="n">
+        <v>0.08</v>
       </c>
       <c r="J16" s="23" t="n"/>
       <c r="K16" s="23" t="n"/>
@@ -2179,27 +2380,32 @@
         </is>
       </c>
       <c r="C17" s="43" t="n"/>
-      <c r="D17" s="82" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="83" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F17" s="83" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G17" s="83" t="n">
-        <v>2028</v>
-      </c>
-      <c r="H17" s="83" t="n">
-        <v>2029</v>
-      </c>
-      <c r="I17" s="83" t="n">
-        <v>2030</v>
-      </c>
-      <c r="J17" s="82" t="inlineStr">
+      <c r="E17" s="83">
+        <f>YEAR(E18)</f>
+        <v/>
+      </c>
+      <c r="F17" s="83">
+        <f>YEAR(F18)</f>
+        <v/>
+      </c>
+      <c r="G17" s="83">
+        <f>YEAR(G18)</f>
+        <v/>
+      </c>
+      <c r="H17" s="83">
+        <f>YEAR(H18)</f>
+        <v/>
+      </c>
+      <c r="I17" s="83">
+        <f>YEAR(I18)</f>
+        <v/>
+      </c>
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -2222,26 +2428,33 @@
         </is>
       </c>
       <c r="C18" s="23" t="n"/>
-      <c r="D18" s="84" t="n">
-        <v>45930</v>
-      </c>
-      <c r="E18" s="84" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" s="84" t="n">
-        <v>46660</v>
-      </c>
-      <c r="G18" s="84" t="n">
-        <v>47026</v>
-      </c>
-      <c r="H18" s="84" t="n">
-        <v>47391</v>
-      </c>
-      <c r="I18" s="84" t="n">
-        <v>47756</v>
-      </c>
-      <c r="J18" s="85" t="n">
-        <v>47756</v>
+      <c r="D18" s="84">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="E18" s="84">
+        <f>DATE(YEAR($D$10)+E19,9,30)</f>
+        <v/>
+      </c>
+      <c r="F18" s="84">
+        <f>DATE(YEAR($D$10)+F19,9,30)</f>
+        <v/>
+      </c>
+      <c r="G18" s="84">
+        <f>DATE(YEAR($D$10)+G19,9,30)</f>
+        <v/>
+      </c>
+      <c r="H18" s="84">
+        <f>DATE(YEAR($D$10)+H19,9,30)</f>
+        <v/>
+      </c>
+      <c r="I18" s="84">
+        <f>DATE(YEAR($D$10)+I19,9,30)</f>
+        <v/>
+      </c>
+      <c r="J18" s="84">
+        <f>I18</f>
+        <v/>
       </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="23" t="inlineStr">
@@ -2250,8 +2463,9 @@
         </is>
       </c>
       <c r="M18" s="23" t="n"/>
-      <c r="N18" s="86" t="n">
-        <v>18113172.1</v>
+      <c r="N18" s="85">
+        <f>(I26*(1+D7))/(D6-D7)</f>
+        <v/>
       </c>
       <c r="O18" s="23" t="n"/>
     </row>
@@ -2264,20 +2478,24 @@
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="37" t="n"/>
-      <c r="E19" s="87" t="n">
+      <c r="E19" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="88" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="88" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="88" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="88" t="n">
-        <v>5</v>
+      <c r="F19" s="83">
+        <f>E19+1</f>
+        <v/>
+      </c>
+      <c r="G19" s="83">
+        <f>F19+1</f>
+        <v/>
+      </c>
+      <c r="H19" s="83">
+        <f>G19+1</f>
+        <v/>
+      </c>
+      <c r="I19" s="83">
+        <f>H19+1</f>
+        <v/>
       </c>
       <c r="J19" s="37" t="n"/>
       <c r="K19" s="23" t="n"/>
@@ -2287,8 +2505,9 @@
         </is>
       </c>
       <c r="M19" s="23" t="n"/>
-      <c r="N19" s="86" t="n">
-        <v>34250977</v>
+      <c r="N19" s="85">
+        <f>D8*(I21+I23)</f>
+        <v/>
       </c>
       <c r="O19" s="23" t="n"/>
     </row>
@@ -2301,20 +2520,25 @@
       </c>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="23" t="n"/>
-      <c r="E20" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>1.0027</v>
-      </c>
-      <c r="H20" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="89" t="n">
-        <v>1</v>
+      <c r="E20" s="87">
+        <f>YEARFRAC(D18,E18)</f>
+        <v/>
+      </c>
+      <c r="F20" s="87">
+        <f>YEARFRAC(E18,F18)</f>
+        <v/>
+      </c>
+      <c r="G20" s="87">
+        <f>YEARFRAC(F18,G18)</f>
+        <v/>
+      </c>
+      <c r="H20" s="87">
+        <f>YEARFRAC(G18,H18)</f>
+        <v/>
+      </c>
+      <c r="I20" s="87">
+        <f>YEARFRAC(H18,I18)</f>
+        <v/>
       </c>
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="23" t="n"/>
@@ -2324,8 +2548,9 @@
         </is>
       </c>
       <c r="M20" s="23" t="n"/>
-      <c r="N20" s="90" t="n">
-        <v>26182074.6</v>
+      <c r="N20" s="88">
+        <f>AVERAGE(N18:N19)</f>
+        <v/>
       </c>
       <c r="O20" s="23" t="n"/>
     </row>
@@ -2333,25 +2558,30 @@
       <c r="A21" s="23" t="n"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>EBIT (= Operating income path)</t>
+          <t>EBIT (formula from D3 &amp; growth row 4)</t>
         </is>
       </c>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
-      <c r="E21" s="79" t="n">
-        <v>1031318.4</v>
-      </c>
-      <c r="F21" s="79" t="n">
-        <v>1149880.5</v>
-      </c>
-      <c r="G21" s="79" t="n">
-        <v>1270112.3</v>
-      </c>
-      <c r="H21" s="79" t="n">
-        <v>1398473.3</v>
-      </c>
-      <c r="I21" s="79" t="n">
-        <v>1533659.6</v>
+      <c r="E21" s="89">
+        <f>$D$3*(1+E4)</f>
+        <v/>
+      </c>
+      <c r="F21" s="89">
+        <f>E21*(1+F4)</f>
+        <v/>
+      </c>
+      <c r="G21" s="89">
+        <f>F21*(1+G4)</f>
+        <v/>
+      </c>
+      <c r="H21" s="89">
+        <f>G21*(1+H4)</f>
+        <v/>
+      </c>
+      <c r="I21" s="89">
+        <f>H21*(1+I4)</f>
+        <v/>
       </c>
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
@@ -2364,25 +2594,30 @@
       <c r="A22" s="23" t="n"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Less: Cash Taxes</t>
+          <t>Less: Cash Taxes (=EBIT × tax rate)</t>
         </is>
       </c>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="86" t="n">
-        <v>193580.9</v>
-      </c>
-      <c r="F22" s="86" t="n">
-        <v>215835.3</v>
-      </c>
-      <c r="G22" s="86" t="n">
-        <v>238403.1</v>
-      </c>
-      <c r="H22" s="86" t="n">
-        <v>262496.8</v>
-      </c>
-      <c r="I22" s="86" t="n">
-        <v>287871.6</v>
+      <c r="E22" s="85">
+        <f>E21*$D$5</f>
+        <v/>
+      </c>
+      <c r="F22" s="85">
+        <f>F21*$D$5</f>
+        <v/>
+      </c>
+      <c r="G22" s="85">
+        <f>G21*$D$5</f>
+        <v/>
+      </c>
+      <c r="H22" s="85">
+        <f>H21*$D$5</f>
+        <v/>
+      </c>
+      <c r="I22" s="85">
+        <f>I21*$D$5</f>
+        <v/>
       </c>
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
@@ -2395,25 +2630,30 @@
       <c r="A23" s="23" t="n"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Plus: D&amp;A</t>
+          <t>Plus: D&amp;A (scales with EBIT)</t>
         </is>
       </c>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="79" t="n">
-        <v>16746.2</v>
-      </c>
-      <c r="F23" s="79" t="n">
-        <v>18420.9</v>
-      </c>
-      <c r="G23" s="79" t="n">
-        <v>20078.7</v>
-      </c>
-      <c r="H23" s="79" t="n">
-        <v>21685</v>
-      </c>
-      <c r="I23" s="79" t="n">
-        <v>23203</v>
+      <c r="E23" s="89">
+        <f>$E$3*E21/$D$3</f>
+        <v/>
+      </c>
+      <c r="F23" s="89">
+        <f>$E$3*F21/$D$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="89">
+        <f>$E$3*G21/$D$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="89">
+        <f>$E$3*H21/$D$3</f>
+        <v/>
+      </c>
+      <c r="I23" s="89">
+        <f>$E$3*I21/$D$3</f>
+        <v/>
       </c>
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="23" t="n"/>
@@ -2426,25 +2666,30 @@
       <c r="A24" s="23" t="n"/>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Less: Capex (grows w/ rev)</t>
+          <t>Less: Capex (=D15×(1+D16)^period)</t>
         </is>
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="91" t="n">
-        <v>42559.6</v>
-      </c>
-      <c r="F24" s="91" t="n">
-        <v>45964.3</v>
-      </c>
-      <c r="G24" s="91" t="n">
-        <v>49641.5</v>
-      </c>
-      <c r="H24" s="91" t="n">
-        <v>53612.8</v>
-      </c>
-      <c r="I24" s="91" t="n">
-        <v>57901.8</v>
+      <c r="E24" s="85">
+        <f>$D$15*(1+$D$16)^E19</f>
+        <v/>
+      </c>
+      <c r="F24" s="85">
+        <f>$D$15*(1+$D$16)^F19</f>
+        <v/>
+      </c>
+      <c r="G24" s="85">
+        <f>$D$15*(1+$D$16)^G19</f>
+        <v/>
+      </c>
+      <c r="H24" s="85">
+        <f>$D$15*(1+$D$16)^H19</f>
+        <v/>
+      </c>
+      <c r="I24" s="85">
+        <f>$D$15*(1+$D$16)^I19</f>
+        <v/>
       </c>
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
@@ -2457,25 +2702,30 @@
       <c r="A25" s="23" t="n"/>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Less: Changes in NWC</t>
+          <t>Less: ΔNWC (formula on EBIT change)</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="79" t="n">
-        <v>59620</v>
-      </c>
-      <c r="F25" s="79" t="n">
-        <v>55645.3</v>
-      </c>
-      <c r="G25" s="79" t="n">
-        <v>55088.8</v>
-      </c>
-      <c r="H25" s="79" t="n">
-        <v>53375</v>
-      </c>
-      <c r="I25" s="79" t="n">
-        <v>50439.3</v>
+      <c r="E25" s="89">
+        <f>MAX(0,E21-$D$3)*0.05</f>
+        <v/>
+      </c>
+      <c r="F25" s="89">
+        <f>MAX(0,F21-E21)*0.05</f>
+        <v/>
+      </c>
+      <c r="G25" s="89">
+        <f>MAX(0,G21-F21)*0.05</f>
+        <v/>
+      </c>
+      <c r="H25" s="89">
+        <f>MAX(0,H21-G21)*0.05</f>
+        <v/>
+      </c>
+      <c r="I25" s="89">
+        <f>MAX(0,I21-H21)*0.05</f>
+        <v/>
       </c>
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
@@ -2488,25 +2738,30 @@
       <c r="A26" s="23" t="n"/>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Unlevered FCF</t>
+          <t>Unlevered FCF (=EBIT-Tax+D&amp;A-Capex-ΔNWC)</t>
         </is>
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="90" t="n">
-        <v>752304.2</v>
-      </c>
-      <c r="F26" s="90" t="n">
-        <v>850856.4</v>
-      </c>
-      <c r="G26" s="90" t="n">
-        <v>947057.6</v>
-      </c>
-      <c r="H26" s="90" t="n">
-        <v>1050673.8</v>
-      </c>
-      <c r="I26" s="90" t="n">
-        <v>1160649.9</v>
+      <c r="E26" s="88">
+        <f>E21-E22+E23-E24-E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="88">
+        <f>F21-F22+F23-F24-F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="88">
+        <f>G21-G22+G23-G24-G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="88">
+        <f>H21-H22+H23-H24-H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="88">
+        <f>I21-I22+I23-I24-I25</f>
+        <v/>
       </c>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
@@ -2523,16 +2778,18 @@
         </is>
       </c>
       <c r="C27" s="23" t="n"/>
-      <c r="D27" s="86" t="n">
-        <v>-27873945.7</v>
+      <c r="D27" s="85">
+        <f>-I35</f>
+        <v/>
       </c>
       <c r="E27" s="23" t="n"/>
       <c r="F27" s="23" t="n"/>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="23" t="n"/>
       <c r="I27" s="23" t="n"/>
-      <c r="J27" s="86" t="n">
-        <v>26182074.6</v>
+      <c r="J27" s="85">
+        <f>N20</f>
+        <v/>
       </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
@@ -2551,23 +2808,29 @@
       <c r="D28" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="90" t="n">
-        <v>752304.2</v>
-      </c>
-      <c r="F28" s="90" t="n">
-        <v>850856.4</v>
-      </c>
-      <c r="G28" s="90" t="n">
-        <v>949652.3</v>
-      </c>
-      <c r="H28" s="90" t="n">
-        <v>1050673.8</v>
-      </c>
-      <c r="I28" s="90" t="n">
-        <v>1160649.9</v>
-      </c>
-      <c r="J28" s="90" t="n">
-        <v>26182074.6</v>
+      <c r="E28" s="88">
+        <f>(E27+E26)*E20</f>
+        <v/>
+      </c>
+      <c r="F28" s="88">
+        <f>(F27+F26)*F20</f>
+        <v/>
+      </c>
+      <c r="G28" s="88">
+        <f>(G27+G26)*G20</f>
+        <v/>
+      </c>
+      <c r="H28" s="88">
+        <f>(H27+H26)*H20</f>
+        <v/>
+      </c>
+      <c r="I28" s="88">
+        <f>(I27+I26)*I20</f>
+        <v/>
+      </c>
+      <c r="J28" s="88">
+        <f>J27+J26</f>
+        <v/>
       </c>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -2583,26 +2846,33 @@
         </is>
       </c>
       <c r="C29" s="23" t="n"/>
-      <c r="D29" s="86" t="n">
-        <v>-27873945.7</v>
-      </c>
-      <c r="E29" s="86" t="n">
-        <v>752304.2</v>
-      </c>
-      <c r="F29" s="86" t="n">
-        <v>850856.4</v>
-      </c>
-      <c r="G29" s="86" t="n">
-        <v>949652.3</v>
-      </c>
-      <c r="H29" s="86" t="n">
-        <v>1050673.8</v>
-      </c>
-      <c r="I29" s="86" t="n">
-        <v>1160649.9</v>
-      </c>
-      <c r="J29" s="86" t="n">
-        <v>26182074.6</v>
+      <c r="D29" s="85">
+        <f>D27+D26</f>
+        <v/>
+      </c>
+      <c r="E29" s="85">
+        <f>(E27+E26)*E20</f>
+        <v/>
+      </c>
+      <c r="F29" s="85">
+        <f>(F27+F26)*F20</f>
+        <v/>
+      </c>
+      <c r="G29" s="85">
+        <f>(G27+G26)*G20</f>
+        <v/>
+      </c>
+      <c r="H29" s="85">
+        <f>(H27+H26)*H20</f>
+        <v/>
+      </c>
+      <c r="I29" s="85">
+        <f>(I27+I26)*I20</f>
+        <v/>
+      </c>
+      <c r="J29" s="85">
+        <f>J27</f>
+        <v/>
       </c>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
@@ -2660,8 +2930,9 @@
         </is>
       </c>
       <c r="C32" s="23" t="n"/>
-      <c r="D32" s="86" t="n">
-        <v>20127310.6</v>
+      <c r="D32" s="85">
+        <f>XNPV(D6,D28:J28,D18:J18)</f>
+        <v/>
       </c>
       <c r="E32" s="23" t="n"/>
       <c r="G32" s="23" t="inlineStr">
@@ -2670,8 +2941,9 @@
         </is>
       </c>
       <c r="H32" s="23" t="n"/>
-      <c r="I32" s="86" t="n">
-        <v>22596093.7</v>
+      <c r="I32" s="85">
+        <f>D12*D11</f>
+        <v/>
       </c>
       <c r="J32" s="23" t="n"/>
       <c r="L32" s="23" t="inlineStr">
@@ -2680,8 +2952,9 @@
         </is>
       </c>
       <c r="M32" s="23" t="n"/>
-      <c r="N32" s="92" t="n">
-        <v>-0.3428</v>
+      <c r="N32" s="91">
+        <f>D37/I37-1</f>
+        <v/>
       </c>
       <c r="O32" s="23" t="n"/>
     </row>
@@ -2693,8 +2966,9 @@
         </is>
       </c>
       <c r="C33" s="23" t="n"/>
-      <c r="D33" s="86" t="n">
-        <v>304537</v>
+      <c r="D33" s="85">
+        <f>+D14</f>
+        <v/>
       </c>
       <c r="E33" s="23" t="n"/>
       <c r="G33" s="23" t="inlineStr">
@@ -2703,8 +2977,9 @@
         </is>
       </c>
       <c r="H33" s="23" t="n"/>
-      <c r="I33" s="86" t="n">
-        <v>5582389</v>
+      <c r="I33" s="85">
+        <f>D13</f>
+        <v/>
       </c>
       <c r="J33" s="23" t="n"/>
       <c r="L33" s="23" t="inlineStr">
@@ -2713,8 +2988,9 @@
         </is>
       </c>
       <c r="M33" s="23" t="n"/>
-      <c r="N33" s="92" t="n">
-        <v>0.0224</v>
+      <c r="N33" s="91">
+        <f>XIRR(D29:J29,D18:J18)</f>
+        <v/>
       </c>
       <c r="O33" s="23" t="n"/>
     </row>
@@ -2726,8 +3002,9 @@
         </is>
       </c>
       <c r="C34" s="23" t="n"/>
-      <c r="D34" s="86" t="n">
-        <v>5582389</v>
+      <c r="D34" s="85">
+        <f>+D13</f>
+        <v/>
       </c>
       <c r="E34" s="23" t="n"/>
       <c r="G34" s="23" t="inlineStr">
@@ -2736,8 +3013,9 @@
         </is>
       </c>
       <c r="H34" s="23" t="n"/>
-      <c r="I34" s="86" t="n">
-        <v>304537</v>
+      <c r="I34" s="85">
+        <f>+D14</f>
+        <v/>
       </c>
       <c r="J34" s="23" t="n"/>
       <c r="L34" s="23" t="n"/>
@@ -2753,8 +3031,9 @@
         </is>
       </c>
       <c r="C35" s="23" t="n"/>
-      <c r="D35" s="90" t="n">
-        <v>14849458.6</v>
+      <c r="D35" s="88">
+        <f>D32+D33-D34</f>
+        <v/>
       </c>
       <c r="E35" s="23" t="n"/>
       <c r="G35" s="23" t="inlineStr">
@@ -2763,8 +3042,9 @@
         </is>
       </c>
       <c r="H35" s="23" t="n"/>
-      <c r="I35" s="90" t="n">
-        <v>27873945.7</v>
+      <c r="I35" s="88">
+        <f>I32+I33-I34</f>
+        <v/>
       </c>
       <c r="J35" s="23" t="n"/>
       <c r="L35" s="42" t="inlineStr">
@@ -2784,7 +3064,7 @@
       <c r="E36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="23" t="n"/>
-      <c r="I36" s="93" t="n"/>
+      <c r="I36" s="92" t="n"/>
       <c r="J36" s="23" t="n"/>
       <c r="L36" s="23" t="inlineStr">
         <is>
@@ -2792,8 +3072,9 @@
         </is>
       </c>
       <c r="M36" s="23" t="n"/>
-      <c r="N36" s="94" t="n">
-        <v>1046.23</v>
+      <c r="N36" s="93">
+        <f>I37</f>
+        <v/>
       </c>
       <c r="O36" s="23" t="n"/>
     </row>
@@ -2805,8 +3086,9 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="94" t="n">
-        <v>687.55</v>
+      <c r="D37" s="93">
+        <f>D35/D12</f>
+        <v/>
       </c>
       <c r="E37" s="23" t="n"/>
       <c r="G37" s="23" t="inlineStr">
@@ -2815,8 +3097,9 @@
         </is>
       </c>
       <c r="H37" s="23" t="n"/>
-      <c r="I37" s="94" t="n">
-        <v>1046.23</v>
+      <c r="I37" s="93">
+        <f>D11</f>
+        <v/>
       </c>
       <c r="J37" s="23" t="n"/>
       <c r="L37" s="23" t="inlineStr">
@@ -2825,8 +3108,9 @@
         </is>
       </c>
       <c r="M37" s="23" t="n"/>
-      <c r="N37" s="94" t="n">
-        <v>-358.68</v>
+      <c r="N37" s="93">
+        <f>D37-I37</f>
+        <v/>
       </c>
       <c r="O37" s="23" t="n"/>
     </row>
@@ -2846,8 +3130,9 @@
         </is>
       </c>
       <c r="M38" s="23" t="n"/>
-      <c r="N38" s="94" t="n">
-        <v>687.55</v>
+      <c r="N38" s="93">
+        <f>SUM(N36:N37)</f>
+        <v/>
       </c>
       <c r="O38" s="23" t="n"/>
     </row>
@@ -3031,9 +3316,9 @@
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="23" t="n"/>
-      <c r="B50" s="95" t="inlineStr">
-        <is>
-          <t>Base FY25 OpInc=924,850 D&amp;A=14,952 Capex=39,407. WACC=9.6% g=3% EV/EBITDA=22x. Source: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+      <c r="B50" s="94" t="inlineStr">
+        <is>
+          <t>Open Formula_Map sheet for the dependency list. Press F9 if needed.</t>
         </is>
       </c>
       <c r="C50" s="23" t="n"/>

--- a/FICO/DCF_FICO.xlsx
+++ b/FICO/DCF_FICO.xlsx
@@ -6,9 +6,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="685" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Formula_Map" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cover Page" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DCF Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cover Page" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DCF Model" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'DCF Model'!$L$36:$L$38</definedName>
@@ -44,9 +43,9 @@
     <definedName name="IQ_WEEK" hidden="1">50000</definedName>
     <definedName name="IQ_YTD" hidden="1">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Cover Page'!$A$1:$P$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover Page'!$A$1:$P$25</definedName>
   </definedNames>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="10000"/>
 </workbook>
 </file>
 
@@ -64,7 +63,7 @@
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="173" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -236,7 +235,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -244,24 +242,8 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000563C1"/>
-      <u val="single"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -302,11 +284,6 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -336,7 +313,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -447,12 +424,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
@@ -478,17 +449,15 @@
     <xf numFmtId="3" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="172" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="1" fontId="25" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="172" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="3" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="2" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="26" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="25" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="170" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="4" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="4" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="8">
@@ -519,7 +488,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Unlevered FCF (formula-driven)</a:t>
+              <a:t>Unlevered FCF (FY2026–2030)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -570,21 +539,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>USD thousands</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -597,6 +551,520 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>FICO model</author>
+  </authors>
+  <commentList>
+    <comment ref="E17" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEAR(E18)</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEAR(F18)</t>
+      </text>
+    </comment>
+    <comment ref="G17" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEAR(G18)</t>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEAR(H18)</t>
+      </text>
+    </comment>
+    <comment ref="I17" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEAR(I18)</t>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D9</t>
+      </text>
+    </comment>
+    <comment ref="E18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=DATE(YEAR($D$10)+E19,9,30)</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=DATE(YEAR($D$10)+F19,9,30)</t>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=DATE(YEAR($D$10)+G19,9,30)</t>
+      </text>
+    </comment>
+    <comment ref="H18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=DATE(YEAR($D$10)+H19,9,30)</t>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=DATE(YEAR($D$10)+I19,9,30)</t>
+      </text>
+    </comment>
+    <comment ref="J18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I18</t>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(I26*(1+D7))/(D6-D7)</t>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+1</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E19+1</t>
+      </text>
+    </comment>
+    <comment ref="G19" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E19+1</t>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E19+1</t>
+      </text>
+    </comment>
+    <comment ref="I19" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E19+1</t>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D8*(I21+I23)</t>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEARFRAC(prior,E18)</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEARFRAC(prior,F18)</t>
+      </text>
+    </comment>
+    <comment ref="G20" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEARFRAC(prior,G18)</t>
+      </text>
+    </comment>
+    <comment ref="H20" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEARFRAC(prior,H18)</t>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=YEARFRAC(prior,I18)</t>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=AVERAGE(N18:N19)</t>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$D$3*(1+E4)</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E21*(1+F4)</t>
+      </text>
+    </comment>
+    <comment ref="G21" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F21*(1+G4)</t>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G21*(1+H4)</t>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H21*(1+I4)</t>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E21*$D$5</t>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F21*$D$5</t>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G21*$D$5</t>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H21*$D$5</t>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I21*$D$5</t>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$E$3*E21/$D$3</t>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$E$3*F21/$D$3</t>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$E$3*G21/$D$3</t>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$E$3*H21/$D$3</t>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$E$3*I21/$D$3</t>
+      </text>
+    </comment>
+    <comment ref="E24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$D$15*(1+$D$16)^E19</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$D$15*(1+$D$16)^F19</t>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$D$15*(1+$D$16)^G19</t>
+      </text>
+    </comment>
+    <comment ref="H24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$D$15*(1+$D$16)^H19</t>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=$D$15*(1+$D$16)^I19</t>
+      </text>
+    </comment>
+    <comment ref="E25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=MAX(0,ΔEBIT)*5%</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=MAX(0,ΔEBIT)*5%</t>
+      </text>
+    </comment>
+    <comment ref="G25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=MAX(0,ΔEBIT)*5%</t>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=MAX(0,ΔEBIT)*5%</t>
+      </text>
+    </comment>
+    <comment ref="I25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=MAX(0,ΔEBIT)*5%</t>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E21-E22+E23-E24-E25</t>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F21-F22+F23-F24-F25</t>
+      </text>
+    </comment>
+    <comment ref="G26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G21-G22+G23-G24-G25</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H21-H22+H23-H24-H25</t>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I21-I22+I23-I24-I25</t>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=-I35</t>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N20</t>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(E27+E26)*E20</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(F27+F26)*F20</t>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(G27+G26)*G20</t>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(H27+H26)*H20</t>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(I27+I26)*I20</t>
+      </text>
+    </comment>
+    <comment ref="J28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J27+J26</t>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D27+D26</t>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(E27+E26)*E20</t>
+      </text>
+    </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(F27+F26)*F20</t>
+      </text>
+    </comment>
+    <comment ref="G29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(G27+G26)*G20</t>
+      </text>
+    </comment>
+    <comment ref="H29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(H27+H26)*H20</t>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(I27+I26)*I20</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J27</t>
+      </text>
+    </comment>
+    <comment ref="D32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=XNPV(D6,D28:J28,D18:J18)</t>
+      </text>
+    </comment>
+    <comment ref="I32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D12*D11</t>
+      </text>
+    </comment>
+    <comment ref="N32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D37/I37-1</t>
+      </text>
+    </comment>
+    <comment ref="D33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D14</t>
+      </text>
+    </comment>
+    <comment ref="I33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D13</t>
+      </text>
+    </comment>
+    <comment ref="D34" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D13</t>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D14</t>
+      </text>
+    </comment>
+    <comment ref="D35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D32+D33-D34</t>
+      </text>
+    </comment>
+    <comment ref="I35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I32+I33-I34</t>
+      </text>
+    </comment>
+    <comment ref="N36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I37</t>
+      </text>
+    </comment>
+    <comment ref="D37" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D35/D12</t>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D11</t>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D37-I37</t>
+      </text>
+    </comment>
+    <comment ref="N38" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(N36:N37)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -893,565 +1361,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="68" t="inlineStr">
-        <is>
-          <t>Updated math — Excel formula dependencies (not typed results)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Yellow cells = inputs. Green/white formula cells = depend on other rows/sheets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="69" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B4" s="69" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="C4" s="69" t="inlineStr">
-        <is>
-          <t>Excel formula / dependency</t>
-        </is>
-      </c>
-      <c r="D4" s="69" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="70" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B5" s="70" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C5" s="70" t="inlineStr">
-        <is>
-          <t>input (or ='03_Three_Statement'!J13 if joined)</t>
-        </is>
-      </c>
-      <c r="D5" s="70" t="inlineStr">
-        <is>
-          <t>FY25 ETR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="70" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="B6" s="70" t="inlineStr">
-        <is>
-          <t>E17:I17</t>
-        </is>
-      </c>
-      <c r="C6" s="70">
-        <f>YEAR(E18) …</f>
-        <v/>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>Depends on date row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="70" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="B7" s="70" t="inlineStr">
-        <is>
-          <t>E18:I18</t>
-        </is>
-      </c>
-      <c r="C7" s="70">
-        <f>DATE(YEAR($D$10)+E19,9,30)</f>
-        <v/>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
-        <is>
-          <t>Depends on FYE + period</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="70" t="inlineStr">
-        <is>
-          <t>Periods</t>
-        </is>
-      </c>
-      <c r="B8" s="70" t="inlineStr">
-        <is>
-          <t>F19:I19</t>
-        </is>
-      </c>
-      <c r="C8" s="70">
-        <f>E19+1 …</f>
-        <v/>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
-        <is>
-          <t>Depends on prior period</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="70" t="inlineStr">
-        <is>
-          <t>Year fraction</t>
-        </is>
-      </c>
-      <c r="B9" s="70" t="inlineStr">
-        <is>
-          <t>E20:I20</t>
-        </is>
-      </c>
-      <c r="C9" s="70">
-        <f>YEARFRAC(prior_date, date)</f>
-        <v/>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Discount stub</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="70" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B10" s="70" t="inlineStr">
-        <is>
-          <t>E21:I21</t>
-        </is>
-      </c>
-      <c r="C10" s="70" t="inlineStr">
-        <is>
-          <t>Standalone: =$D$3*(1+E4) then rolls; Joined: 3-stmt GP−opex−DA</t>
-        </is>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Operating income path</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="70" t="inlineStr">
-        <is>
-          <t>Cash Taxes</t>
-        </is>
-      </c>
-      <c r="B11" s="70" t="inlineStr">
-        <is>
-          <t>E22:I22</t>
-        </is>
-      </c>
-      <c r="C11" s="70">
-        <f>E21*$D$5</f>
-        <v/>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>Depends on EBIT and tax rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="70" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B12" s="70" t="inlineStr">
-        <is>
-          <t>E23:I23</t>
-        </is>
-      </c>
-      <c r="C12" s="70" t="inlineStr">
-        <is>
-          <t>Standalone: =$E$3*E21/$D$3; Joined: ='03_Three_Statement'!J30</t>
-        </is>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>Depends on EBIT or 3-stmt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="70" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="B13" s="70" t="inlineStr">
-        <is>
-          <t>E24:I24</t>
-        </is>
-      </c>
-      <c r="C13" s="70" t="inlineStr">
-        <is>
-          <t>Standalone: =$D$15*(1+$D$16)^E19; Joined: 3-stmt!J68</t>
-        </is>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Depends on base capex/growth or 3-stmt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="70" t="inlineStr">
-        <is>
-          <t>ΔNWC</t>
-        </is>
-      </c>
-      <c r="B14" s="70" t="inlineStr">
-        <is>
-          <t>E25:I25</t>
-        </is>
-      </c>
-      <c r="C14" s="70" t="inlineStr">
-        <is>
-          <t>Standalone: =MAX(0,ΔEBIT)*5%; Joined: 3-stmt!J89</t>
-        </is>
-      </c>
-      <c r="D14" s="70" t="inlineStr">
-        <is>
-          <t>WC investment</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="70" t="inlineStr">
-        <is>
-          <t>Unlevered FCF</t>
-        </is>
-      </c>
-      <c r="B15" s="70" t="inlineStr">
-        <is>
-          <t>E26:I26</t>
-        </is>
-      </c>
-      <c r="C15" s="70">
-        <f>EBIT − Tax + D&amp;A − Capex − ΔNWC</f>
-        <v/>
-      </c>
-      <c r="D15" s="70" t="inlineStr">
-        <is>
-          <t>Core FCF identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="70" t="inlineStr">
-        <is>
-          <t>TV (PG)</t>
-        </is>
-      </c>
-      <c r="B16" s="70" t="inlineStr">
-        <is>
-          <t>N18</t>
-        </is>
-      </c>
-      <c r="C16" s="70">
-        <f>(I26*(1+D7))/(D6-D7)</f>
-        <v/>
-      </c>
-      <c r="D16" s="70" t="inlineStr">
-        <is>
-          <t>Gordon growth on final UFCF</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="70" t="inlineStr">
-        <is>
-          <t>TV (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="B17" s="70" t="inlineStr">
-        <is>
-          <t>N19</t>
-        </is>
-      </c>
-      <c r="C17" s="70">
-        <f>D8*(I21+I23)</f>
-        <v/>
-      </c>
-      <c r="D17" s="70" t="inlineStr">
-        <is>
-          <t>Exit multiple on final EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="70" t="inlineStr">
-        <is>
-          <t>TV Average</t>
-        </is>
-      </c>
-      <c r="B18" s="70" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="C18" s="70">
-        <f>AVERAGE(N18:N19)</f>
-        <v/>
-      </c>
-      <c r="D18" s="70" t="inlineStr">
-        <is>
-          <t>Blended exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="70" t="inlineStr">
-        <is>
-          <t>Enterprise Value</t>
-        </is>
-      </c>
-      <c r="B19" s="70" t="inlineStr">
-        <is>
-          <t>D32</t>
-        </is>
-      </c>
-      <c r="C19" s="70">
-        <f>XNPV(D6,D28:J28,D18:J18)</f>
-        <v/>
-      </c>
-      <c r="D19" s="70" t="inlineStr">
-        <is>
-          <t>PV of transaction CFs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="70" t="inlineStr">
-        <is>
-          <t>Equity Value</t>
-        </is>
-      </c>
-      <c r="B20" s="70" t="inlineStr">
-        <is>
-          <t>D35</t>
-        </is>
-      </c>
-      <c r="C20" s="70">
-        <f>D32+D33−D34</f>
-        <v/>
-      </c>
-      <c r="D20" s="70" t="inlineStr">
-        <is>
-          <t>EV + cash − debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="70" t="inlineStr">
-        <is>
-          <t>Equity / share</t>
-        </is>
-      </c>
-      <c r="B21" s="70" t="inlineStr">
-        <is>
-          <t>D37</t>
-        </is>
-      </c>
-      <c r="C21" s="70">
-        <f>D35/D12</f>
-        <v/>
-      </c>
-      <c r="D21" s="70" t="inlineStr">
-        <is>
-          <t>Depends on equity &amp; shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="70" t="inlineStr">
-        <is>
-          <t>3S Revenue fcst</t>
-        </is>
-      </c>
-      <c r="B22" s="70" t="inlineStr">
-        <is>
-          <t>J24</t>
-        </is>
-      </c>
-      <c r="C22" s="70">
-        <f>I24*(1+J7)</f>
-        <v/>
-      </c>
-      <c r="D22" s="70" t="inlineStr">
-        <is>
-          <t>Grows from prior year</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="70" t="inlineStr">
-        <is>
-          <t>3S COGS fcst</t>
-        </is>
-      </c>
-      <c r="B23" s="70" t="inlineStr">
-        <is>
-          <t>J25</t>
-        </is>
-      </c>
-      <c r="C23" s="70">
-        <f>J24*J8</f>
-        <v/>
-      </c>
-      <c r="D23" s="70" t="inlineStr">
-        <is>
-          <t>Depends on revenue &amp; COGS%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="70" t="inlineStr">
-        <is>
-          <t>3S Gross Profit</t>
-        </is>
-      </c>
-      <c r="B24" s="70" t="inlineStr">
-        <is>
-          <t>J26</t>
-        </is>
-      </c>
-      <c r="C24" s="70">
-        <f>J24-J25</f>
-        <v/>
-      </c>
-      <c r="D24" s="70" t="inlineStr">
-        <is>
-          <t>Depends on Rev &amp; COGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="70" t="inlineStr">
-        <is>
-          <t>3S SG&amp;A fcst</t>
-        </is>
-      </c>
-      <c r="B25" s="70" t="inlineStr">
-        <is>
-          <t>J28</t>
-        </is>
-      </c>
-      <c r="C25" s="70">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="D25" s="70" t="inlineStr">
-        <is>
-          <t>Depends on salaries driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="70" t="inlineStr">
-        <is>
-          <t>3S Capex fcst</t>
-        </is>
-      </c>
-      <c r="B26" s="70" t="inlineStr">
-        <is>
-          <t>J68</t>
-        </is>
-      </c>
-      <c r="C26" s="70">
-        <f>J18</f>
-        <v/>
-      </c>
-      <c r="D26" s="70" t="inlineStr">
-        <is>
-          <t>Depends on capex assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="70" t="inlineStr">
-        <is>
-          <t>3S ΔNWC fcst</t>
-        </is>
-      </c>
-      <c r="B27" s="70" t="inlineStr">
-        <is>
-          <t>J89</t>
-        </is>
-      </c>
-      <c r="C27" s="70">
-        <f>J88-I88</f>
-        <v/>
-      </c>
-      <c r="D27" s="70" t="inlineStr">
-        <is>
-          <t>Depends on NWC schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="B30" s="71" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B3:O29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.08984375" defaultRowHeight="14"/>
   <cols>
@@ -1971,7 +1880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1983,18 +1892,18 @@
     <col width="3.54296875" customWidth="1" style="1" min="1" max="1"/>
     <col width="36" customWidth="1" style="1" min="2" max="2"/>
     <col width="12.453125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="15" customWidth="1" style="2" min="4" max="4"/>
-    <col width="15" customWidth="1" style="1" min="5" max="9"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" style="1" min="10" max="14"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="14" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14" customWidth="1" style="1" min="5" max="9"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="1" min="10" max="14"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="9.08984375" customWidth="1" style="1" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2021,13 +1930,13 @@
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>FICO DCF (formula-driven)</t>
+          <t>FICO DCF — all numbers visible; hover green cells for formulas</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
-      <c r="D2" s="72" t="inlineStr">
-        <is>
-          <t>Yellow=inputs. All taxes/UFCF/TV/EV/dates are Excel formulas.</t>
+      <c r="D2" s="68" t="inlineStr">
+        <is>
+          <t>Intrinsic Equity/Share = 652.20</t>
         </is>
       </c>
       <c r="E2" s="7" t="n"/>
@@ -2045,7 +1954,7 @@
       <c r="A3" s="23" t="n"/>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>FY25 OpInc (base)</t>
+          <t>FY25 OpInc</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
@@ -2053,10 +1962,10 @@
           <t>FY25 D&amp;A</t>
         </is>
       </c>
-      <c r="D3" s="73" t="n">
+      <c r="D3" s="69" t="n">
         <v>924850</v>
       </c>
-      <c r="E3" s="74" t="n">
+      <c r="E3" s="70" t="n">
         <v>14952</v>
       </c>
       <c r="F3" s="21" t="n"/>
@@ -2074,24 +1983,24 @@
       <c r="A4" s="23" t="n"/>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>EBIT growth (explicit)</t>
+          <t>EBIT growth</t>
         </is>
       </c>
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="33" t="n"/>
-      <c r="E4" s="75" t="n">
+      <c r="E4" s="71" t="n">
         <v>0.12</v>
       </c>
-      <c r="F4" s="75" t="n">
+      <c r="F4" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="G4" s="75" t="n">
+      <c r="G4" s="71" t="n">
         <v>0.09</v>
       </c>
-      <c r="H4" s="75" t="n">
+      <c r="H4" s="71" t="n">
         <v>0.08</v>
       </c>
-      <c r="I4" s="75" t="n">
+      <c r="I4" s="71" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J4" s="23" t="n"/>
@@ -2109,7 +2018,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="n"/>
-      <c r="D5" s="76" t="n">
+      <c r="D5" s="72" t="n">
         <v>0.1877</v>
       </c>
       <c r="E5" s="21" t="n"/>
@@ -2132,7 +2041,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n"/>
-      <c r="D6" s="77" t="n">
+      <c r="D6" s="73" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="23" t="n"/>
@@ -2155,7 +2064,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n"/>
-      <c r="D7" s="77" t="n">
+      <c r="D7" s="73" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="23" t="n"/>
@@ -2178,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n"/>
-      <c r="D8" s="78" t="n">
+      <c r="D8" s="74" t="n">
         <v>22</v>
       </c>
       <c r="E8" s="23" t="n"/>
@@ -2201,7 +2110,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n"/>
-      <c r="D9" s="79" t="n">
+      <c r="D9" s="75" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="23" t="n"/>
@@ -2224,7 +2133,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n"/>
-      <c r="D10" s="79" t="n">
+      <c r="D10" s="75" t="n">
         <v>45930</v>
       </c>
       <c r="E10" s="23" t="n"/>
@@ -2247,7 +2156,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n"/>
-      <c r="D11" s="80" t="n">
+      <c r="D11" s="76" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="23" t="n"/>
@@ -2270,7 +2179,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n"/>
-      <c r="D12" s="81" t="n">
+      <c r="D12" s="77" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="23" t="n"/>
@@ -2293,7 +2202,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n"/>
-      <c r="D13" s="82" t="n">
+      <c r="D13" s="78" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="23" t="n"/>
@@ -2316,7 +2225,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n"/>
-      <c r="D14" s="82" t="n">
+      <c r="D14" s="78" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="23" t="n"/>
@@ -2339,7 +2248,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n"/>
-      <c r="D15" s="74" t="n">
+      <c r="D15" s="70" t="n">
         <v>39407</v>
       </c>
       <c r="E15" s="23" t="n"/>
@@ -2362,7 +2271,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n"/>
-      <c r="D16" s="75" t="n">
+      <c r="D16" s="71" t="n">
         <v>0.08</v>
       </c>
       <c r="J16" s="23" t="n"/>
@@ -2385,25 +2294,20 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="83">
-        <f>YEAR(E18)</f>
-        <v/>
-      </c>
-      <c r="F17" s="83">
-        <f>YEAR(F18)</f>
-        <v/>
-      </c>
-      <c r="G17" s="83">
-        <f>YEAR(G18)</f>
-        <v/>
-      </c>
-      <c r="H17" s="83">
-        <f>YEAR(H18)</f>
-        <v/>
-      </c>
-      <c r="I17" s="83">
-        <f>YEAR(I18)</f>
-        <v/>
+      <c r="E17" s="79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F17" s="79" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G17" s="79" t="n">
+        <v>2028</v>
+      </c>
+      <c r="H17" s="79" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I17" s="79" t="n">
+        <v>2030</v>
       </c>
       <c r="J17" s="44" t="inlineStr">
         <is>
@@ -2428,33 +2332,26 @@
         </is>
       </c>
       <c r="C18" s="23" t="n"/>
-      <c r="D18" s="84">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="E18" s="84">
-        <f>DATE(YEAR($D$10)+E19,9,30)</f>
-        <v/>
-      </c>
-      <c r="F18" s="84">
-        <f>DATE(YEAR($D$10)+F19,9,30)</f>
-        <v/>
-      </c>
-      <c r="G18" s="84">
-        <f>DATE(YEAR($D$10)+G19,9,30)</f>
-        <v/>
-      </c>
-      <c r="H18" s="84">
-        <f>DATE(YEAR($D$10)+H19,9,30)</f>
-        <v/>
-      </c>
-      <c r="I18" s="84">
-        <f>DATE(YEAR($D$10)+I19,9,30)</f>
-        <v/>
-      </c>
-      <c r="J18" s="84">
-        <f>I18</f>
-        <v/>
+      <c r="D18" s="80" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E18" s="80" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" s="80" t="n">
+        <v>46660</v>
+      </c>
+      <c r="G18" s="80" t="n">
+        <v>47026</v>
+      </c>
+      <c r="H18" s="80" t="n">
+        <v>47391</v>
+      </c>
+      <c r="I18" s="80" t="n">
+        <v>47756</v>
+      </c>
+      <c r="J18" s="80" t="n">
+        <v>47756</v>
       </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="23" t="inlineStr">
@@ -2463,9 +2360,8 @@
         </is>
       </c>
       <c r="M18" s="23" t="n"/>
-      <c r="N18" s="85">
-        <f>(I26*(1+D7))/(D6-D7)</f>
-        <v/>
+      <c r="N18" s="81" t="n">
+        <v>17579122.8</v>
       </c>
       <c r="O18" s="23" t="n"/>
     </row>
@@ -2478,24 +2374,20 @@
       </c>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="37" t="n"/>
-      <c r="E19" s="86" t="n">
+      <c r="E19" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="83">
-        <f>E19+1</f>
-        <v/>
-      </c>
-      <c r="G19" s="83">
-        <f>F19+1</f>
-        <v/>
-      </c>
-      <c r="H19" s="83">
-        <f>G19+1</f>
-        <v/>
-      </c>
-      <c r="I19" s="83">
-        <f>H19+1</f>
-        <v/>
+      <c r="F19" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="79" t="n">
+        <v>5</v>
       </c>
       <c r="J19" s="37" t="n"/>
       <c r="K19" s="23" t="n"/>
@@ -2505,9 +2397,8 @@
         </is>
       </c>
       <c r="M19" s="23" t="n"/>
-      <c r="N19" s="85">
-        <f>D8*(I21+I23)</f>
-        <v/>
+      <c r="N19" s="81" t="n">
+        <v>32085128.6</v>
       </c>
       <c r="O19" s="23" t="n"/>
     </row>
@@ -2520,25 +2411,20 @@
       </c>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="23" t="n"/>
-      <c r="E20" s="87">
-        <f>YEARFRAC(D18,E18)</f>
-        <v/>
-      </c>
-      <c r="F20" s="87">
-        <f>YEARFRAC(E18,F18)</f>
-        <v/>
-      </c>
-      <c r="G20" s="87">
-        <f>YEARFRAC(F18,G18)</f>
-        <v/>
-      </c>
-      <c r="H20" s="87">
-        <f>YEARFRAC(G18,H18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="87">
-        <f>YEARFRAC(H18,I18)</f>
-        <v/>
+      <c r="E20" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="82" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="H20" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="82" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="23" t="n"/>
@@ -2548,9 +2434,8 @@
         </is>
       </c>
       <c r="M20" s="23" t="n"/>
-      <c r="N20" s="88">
-        <f>AVERAGE(N18:N19)</f>
-        <v/>
+      <c r="N20" s="83" t="n">
+        <v>24832125.7</v>
       </c>
       <c r="O20" s="23" t="n"/>
     </row>
@@ -2558,30 +2443,25 @@
       <c r="A21" s="23" t="n"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>EBIT (formula from D3 &amp; growth row 4)</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
-      <c r="E21" s="89">
-        <f>$D$3*(1+E4)</f>
-        <v/>
-      </c>
-      <c r="F21" s="89">
-        <f>E21*(1+F4)</f>
-        <v/>
-      </c>
-      <c r="G21" s="89">
-        <f>F21*(1+G4)</f>
-        <v/>
-      </c>
-      <c r="H21" s="89">
-        <f>G21*(1+H4)</f>
-        <v/>
-      </c>
-      <c r="I21" s="89">
-        <f>H21*(1+I4)</f>
-        <v/>
+      <c r="E21" s="81" t="n">
+        <v>1035832</v>
+      </c>
+      <c r="F21" s="81" t="n">
+        <v>1139415.2</v>
+      </c>
+      <c r="G21" s="81" t="n">
+        <v>1241962.6</v>
+      </c>
+      <c r="H21" s="81" t="n">
+        <v>1341319.6</v>
+      </c>
+      <c r="I21" s="81" t="n">
+        <v>1435211.9</v>
       </c>
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
@@ -2594,30 +2474,25 @@
       <c r="A22" s="23" t="n"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Less: Cash Taxes (=EBIT × tax rate)</t>
+          <t>Less: Cash Taxes</t>
         </is>
       </c>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="85">
-        <f>E21*$D$5</f>
-        <v/>
-      </c>
-      <c r="F22" s="85">
-        <f>F21*$D$5</f>
-        <v/>
-      </c>
-      <c r="G22" s="85">
-        <f>G21*$D$5</f>
-        <v/>
-      </c>
-      <c r="H22" s="85">
-        <f>H21*$D$5</f>
-        <v/>
-      </c>
-      <c r="I22" s="85">
-        <f>I21*$D$5</f>
-        <v/>
+      <c r="E22" s="81" t="n">
+        <v>194425.7</v>
+      </c>
+      <c r="F22" s="81" t="n">
+        <v>213868.2</v>
+      </c>
+      <c r="G22" s="81" t="n">
+        <v>233116.4</v>
+      </c>
+      <c r="H22" s="81" t="n">
+        <v>251765.7</v>
+      </c>
+      <c r="I22" s="81" t="n">
+        <v>269389.3</v>
       </c>
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
@@ -2630,30 +2505,25 @@
       <c r="A23" s="23" t="n"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Plus: D&amp;A (scales with EBIT)</t>
+          <t>Plus: D&amp;A</t>
         </is>
       </c>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="89">
-        <f>$E$3*E21/$D$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="89">
-        <f>$E$3*F21/$D$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="89">
-        <f>$E$3*G21/$D$3</f>
-        <v/>
-      </c>
-      <c r="H23" s="89">
-        <f>$E$3*H21/$D$3</f>
-        <v/>
-      </c>
-      <c r="I23" s="89">
-        <f>$E$3*I21/$D$3</f>
-        <v/>
+      <c r="E23" s="81" t="n">
+        <v>16746.2</v>
+      </c>
+      <c r="F23" s="81" t="n">
+        <v>18420.9</v>
+      </c>
+      <c r="G23" s="81" t="n">
+        <v>20078.7</v>
+      </c>
+      <c r="H23" s="81" t="n">
+        <v>21685</v>
+      </c>
+      <c r="I23" s="81" t="n">
+        <v>23203</v>
       </c>
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="23" t="n"/>
@@ -2666,30 +2536,25 @@
       <c r="A24" s="23" t="n"/>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Less: Capex (=D15×(1+D16)^period)</t>
+          <t>Less: Capex</t>
         </is>
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="85">
-        <f>$D$15*(1+$D$16)^E19</f>
-        <v/>
-      </c>
-      <c r="F24" s="85">
-        <f>$D$15*(1+$D$16)^F19</f>
-        <v/>
-      </c>
-      <c r="G24" s="85">
-        <f>$D$15*(1+$D$16)^G19</f>
-        <v/>
-      </c>
-      <c r="H24" s="85">
-        <f>$D$15*(1+$D$16)^H19</f>
-        <v/>
-      </c>
-      <c r="I24" s="85">
-        <f>$D$15*(1+$D$16)^I19</f>
-        <v/>
+      <c r="E24" s="81" t="n">
+        <v>42559.6</v>
+      </c>
+      <c r="F24" s="81" t="n">
+        <v>45964.3</v>
+      </c>
+      <c r="G24" s="81" t="n">
+        <v>49641.5</v>
+      </c>
+      <c r="H24" s="81" t="n">
+        <v>53612.8</v>
+      </c>
+      <c r="I24" s="81" t="n">
+        <v>57901.8</v>
       </c>
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
@@ -2702,30 +2567,25 @@
       <c r="A25" s="23" t="n"/>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Less: ΔNWC (formula on EBIT change)</t>
+          <t>Less: Changes in NWC</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="89">
-        <f>MAX(0,E21-$D$3)*0.05</f>
-        <v/>
-      </c>
-      <c r="F25" s="89">
-        <f>MAX(0,F21-E21)*0.05</f>
-        <v/>
-      </c>
-      <c r="G25" s="89">
-        <f>MAX(0,G21-F21)*0.05</f>
-        <v/>
-      </c>
-      <c r="H25" s="89">
-        <f>MAX(0,H21-G21)*0.05</f>
-        <v/>
-      </c>
-      <c r="I25" s="89">
-        <f>MAX(0,I21-H21)*0.05</f>
-        <v/>
+      <c r="E25" s="81" t="n">
+        <v>5549.1</v>
+      </c>
+      <c r="F25" s="81" t="n">
+        <v>5179.2</v>
+      </c>
+      <c r="G25" s="81" t="n">
+        <v>5127.4</v>
+      </c>
+      <c r="H25" s="81" t="n">
+        <v>4967.9</v>
+      </c>
+      <c r="I25" s="81" t="n">
+        <v>4694.6</v>
       </c>
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
@@ -2738,30 +2598,25 @@
       <c r="A26" s="23" t="n"/>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Unlevered FCF (=EBIT-Tax+D&amp;A-Capex-ΔNWC)</t>
+          <t>Unlevered FCF</t>
         </is>
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="88">
-        <f>E21-E22+E23-E24-E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="88">
-        <f>F21-F22+F23-F24-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="88">
-        <f>G21-G22+G23-G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="88">
-        <f>H21-H22+H23-H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="88">
-        <f>I21-I22+I23-I24-I25</f>
-        <v/>
+      <c r="E26" s="83" t="n">
+        <v>810043.9</v>
+      </c>
+      <c r="F26" s="83" t="n">
+        <v>892824.3</v>
+      </c>
+      <c r="G26" s="83" t="n">
+        <v>974156.1</v>
+      </c>
+      <c r="H26" s="83" t="n">
+        <v>1052658.3</v>
+      </c>
+      <c r="I26" s="83" t="n">
+        <v>1126429.2</v>
       </c>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
@@ -2778,18 +2633,16 @@
         </is>
       </c>
       <c r="C27" s="23" t="n"/>
-      <c r="D27" s="85">
-        <f>-I35</f>
-        <v/>
+      <c r="D27" s="81" t="n">
+        <v>-27873945.7</v>
       </c>
       <c r="E27" s="23" t="n"/>
       <c r="F27" s="23" t="n"/>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="23" t="n"/>
       <c r="I27" s="23" t="n"/>
-      <c r="J27" s="85">
-        <f>N20</f>
-        <v/>
+      <c r="J27" s="81" t="n">
+        <v>24832125.7</v>
       </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
@@ -2805,32 +2658,26 @@
         </is>
       </c>
       <c r="C28" s="23" t="n"/>
-      <c r="D28" s="90" t="n">
+      <c r="D28" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="88">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F28" s="88">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G28" s="88">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H28" s="88">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I28" s="88">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J28" s="88">
-        <f>J27+J26</f>
-        <v/>
+      <c r="E28" s="83" t="n">
+        <v>810043.9</v>
+      </c>
+      <c r="F28" s="83" t="n">
+        <v>892824.3</v>
+      </c>
+      <c r="G28" s="83" t="n">
+        <v>976825</v>
+      </c>
+      <c r="H28" s="83" t="n">
+        <v>1052658.3</v>
+      </c>
+      <c r="I28" s="83" t="n">
+        <v>1126429.2</v>
+      </c>
+      <c r="J28" s="83" t="n">
+        <v>24832125.7</v>
       </c>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -2846,33 +2693,26 @@
         </is>
       </c>
       <c r="C29" s="23" t="n"/>
-      <c r="D29" s="85">
-        <f>D27+D26</f>
-        <v/>
-      </c>
-      <c r="E29" s="85">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F29" s="85">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G29" s="85">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H29" s="85">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I29" s="85">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J29" s="85">
-        <f>J27</f>
-        <v/>
+      <c r="D29" s="81" t="n">
+        <v>-27873945.7</v>
+      </c>
+      <c r="E29" s="81" t="n">
+        <v>810043.9</v>
+      </c>
+      <c r="F29" s="81" t="n">
+        <v>892824.3</v>
+      </c>
+      <c r="G29" s="81" t="n">
+        <v>976825</v>
+      </c>
+      <c r="H29" s="81" t="n">
+        <v>1052658.3</v>
+      </c>
+      <c r="I29" s="81" t="n">
+        <v>1126429.2</v>
+      </c>
+      <c r="J29" s="81" t="n">
+        <v>24832125.7</v>
       </c>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
@@ -2930,9 +2770,8 @@
         </is>
       </c>
       <c r="C32" s="23" t="n"/>
-      <c r="D32" s="85">
-        <f>XNPV(D6,D28:J28,D18:J18)</f>
-        <v/>
+      <c r="D32" s="81" t="n">
+        <v>19363871.4</v>
       </c>
       <c r="E32" s="23" t="n"/>
       <c r="G32" s="23" t="inlineStr">
@@ -2941,9 +2780,8 @@
         </is>
       </c>
       <c r="H32" s="23" t="n"/>
-      <c r="I32" s="85">
-        <f>D12*D11</f>
-        <v/>
+      <c r="I32" s="81" t="n">
+        <v>22596093.7</v>
       </c>
       <c r="J32" s="23" t="n"/>
       <c r="L32" s="23" t="inlineStr">
@@ -2952,9 +2790,8 @@
         </is>
       </c>
       <c r="M32" s="23" t="n"/>
-      <c r="N32" s="91">
-        <f>D37/I37-1</f>
-        <v/>
+      <c r="N32" s="85" t="n">
+        <v>-0.3766</v>
       </c>
       <c r="O32" s="23" t="n"/>
     </row>
@@ -2966,9 +2803,8 @@
         </is>
       </c>
       <c r="C33" s="23" t="n"/>
-      <c r="D33" s="85">
-        <f>+D14</f>
-        <v/>
+      <c r="D33" s="81" t="n">
+        <v>304537</v>
       </c>
       <c r="E33" s="23" t="n"/>
       <c r="G33" s="23" t="inlineStr">
@@ -2977,9 +2813,8 @@
         </is>
       </c>
       <c r="H33" s="23" t="n"/>
-      <c r="I33" s="85">
-        <f>D13</f>
-        <v/>
+      <c r="I33" s="81" t="n">
+        <v>5582389</v>
       </c>
       <c r="J33" s="23" t="n"/>
       <c r="L33" s="23" t="inlineStr">
@@ -2988,7 +2823,7 @@
         </is>
       </c>
       <c r="M33" s="23" t="n"/>
-      <c r="N33" s="91">
+      <c r="N33" s="46">
         <f>XIRR(D29:J29,D18:J18)</f>
         <v/>
       </c>
@@ -3002,9 +2837,8 @@
         </is>
       </c>
       <c r="C34" s="23" t="n"/>
-      <c r="D34" s="85">
-        <f>+D13</f>
-        <v/>
+      <c r="D34" s="81" t="n">
+        <v>5582389</v>
       </c>
       <c r="E34" s="23" t="n"/>
       <c r="G34" s="23" t="inlineStr">
@@ -3013,9 +2847,8 @@
         </is>
       </c>
       <c r="H34" s="23" t="n"/>
-      <c r="I34" s="85">
-        <f>+D14</f>
-        <v/>
+      <c r="I34" s="81" t="n">
+        <v>304537</v>
       </c>
       <c r="J34" s="23" t="n"/>
       <c r="L34" s="23" t="n"/>
@@ -3031,9 +2864,8 @@
         </is>
       </c>
       <c r="C35" s="23" t="n"/>
-      <c r="D35" s="88">
-        <f>D32+D33-D34</f>
-        <v/>
+      <c r="D35" s="83" t="n">
+        <v>14086019.4</v>
       </c>
       <c r="E35" s="23" t="n"/>
       <c r="G35" s="23" t="inlineStr">
@@ -3042,9 +2874,8 @@
         </is>
       </c>
       <c r="H35" s="23" t="n"/>
-      <c r="I35" s="88">
-        <f>I32+I33-I34</f>
-        <v/>
+      <c r="I35" s="83" t="n">
+        <v>27873945.7</v>
       </c>
       <c r="J35" s="23" t="n"/>
       <c r="L35" s="42" t="inlineStr">
@@ -3064,7 +2895,7 @@
       <c r="E36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="23" t="n"/>
-      <c r="I36" s="92" t="n"/>
+      <c r="I36" s="86" t="n"/>
       <c r="J36" s="23" t="n"/>
       <c r="L36" s="23" t="inlineStr">
         <is>
@@ -3072,9 +2903,8 @@
         </is>
       </c>
       <c r="M36" s="23" t="n"/>
-      <c r="N36" s="93">
-        <f>I37</f>
-        <v/>
+      <c r="N36" s="87" t="n">
+        <v>1046.23</v>
       </c>
       <c r="O36" s="23" t="n"/>
     </row>
@@ -3086,9 +2916,8 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="93">
-        <f>D35/D12</f>
-        <v/>
+      <c r="D37" s="87" t="n">
+        <v>652.2</v>
       </c>
       <c r="E37" s="23" t="n"/>
       <c r="G37" s="23" t="inlineStr">
@@ -3097,9 +2926,8 @@
         </is>
       </c>
       <c r="H37" s="23" t="n"/>
-      <c r="I37" s="93">
-        <f>D11</f>
-        <v/>
+      <c r="I37" s="87" t="n">
+        <v>1046.23</v>
       </c>
       <c r="J37" s="23" t="n"/>
       <c r="L37" s="23" t="inlineStr">
@@ -3108,9 +2936,8 @@
         </is>
       </c>
       <c r="M37" s="23" t="n"/>
-      <c r="N37" s="93">
-        <f>D37-I37</f>
-        <v/>
+      <c r="N37" s="87" t="n">
+        <v>-394.03</v>
       </c>
       <c r="O37" s="23" t="n"/>
     </row>
@@ -3130,9 +2957,8 @@
         </is>
       </c>
       <c r="M38" s="23" t="n"/>
-      <c r="N38" s="93">
-        <f>SUM(N36:N37)</f>
-        <v/>
+      <c r="N38" s="87" t="n">
+        <v>652.2</v>
       </c>
       <c r="O38" s="23" t="n"/>
     </row>
@@ -3316,9 +3142,9 @@
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="23" t="n"/>
-      <c r="B50" s="94" t="inlineStr">
-        <is>
-          <t>Open Formula_Map sheet for the dependency list. Press F9 if needed.</t>
+      <c r="B50" s="88" t="inlineStr">
+        <is>
+          <t>Green=calculated from row dependencies (see comment). 10-K: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
       <c r="C50" s="23" t="n"/>
@@ -3514,5 +3340,6 @@
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="landscape" scale="78"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>